--- a/_review/Potential_Revisione_Traduzioni.xlsx
+++ b/_review/Potential_Revisione_Traduzioni.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-76800" yWindow="-21840" windowWidth="76800" windowHeight="42600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traduzioni" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,26 +25,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00C71617"/>
+      <color rgb="FFC71617"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00999999"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF999999"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C71617"/>
+        <fgColor rgb="FFC71617"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2D5D5"/>
+        <fgColor rgb="FFF2D5D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,35 +85,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,9 +117,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -476,4223 +496,4219 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" style="7" min="1" max="1"/>
+    <col width="34" customWidth="1" style="7" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1" s="7">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Potential — Revisione traduzioni  ·  Modifica le celle di lingua (non la colonna ID). Le righe rosse sono i titoli di sezione (ordine del sito). Simboli &lt;br&gt;/&lt;em&gt; = a capo/evidenziazioni, lasciarli.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Italiano</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>中文</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Русский</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>العربية</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="20" customHeight="1" s="7">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Elementi ricorrenti (scroll, footer)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="7">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>scroll-down</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Scroll Down</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Scorri</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>向下滚动</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Прокрутите вниз</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>مرر للأسفل</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="16" customHeight="1" s="7">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>footer-copy</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>© 2026 Potential. All rights reserved.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>© 2026 Potential. Tutti i diritti riservati.</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>© 2026 Potential. 保留所有权利。</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>© 2026 Potential. Все права защищены.</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>© 2026 Potential. جميع الحقوق محفوظة.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6" ht="16" customHeight="1" s="7">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>footer-privacy</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Privacy Policy</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Informativa sulla Privacy</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>隐私政策</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Политика конфиденциальности</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>سياسة الخصوصية</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>1 · Frase d'apertura</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="8" ht="16" customHeight="1" s="7">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>intro-hl-1</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>One single point</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Un solo punto</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>唯一联络人</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Единая точка</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>نقطة تواصل</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="7">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>intro-hl-2</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>of contact.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>di contatto.</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>所有供应商。</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>контакта.</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>واحدة.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="10" ht="16" customHeight="1" s="7">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>intro-hl-3</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>All suppliers.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Tutti i fornitori.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>一站式对接。</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Все поставщики.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>كلّ الموردين.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="7">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>2 · Aree di competenza</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="12" ht="16" customHeight="1" s="7">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>stag-coverage</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Coverage Areas</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Aree di Copertura</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>覆盖领域</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Области охвата</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>مجالات التغطية</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="13" ht="32" customHeight="1" s="7">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>sectors-hl</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Where we operate.&lt;br&gt;&lt;em&gt;What we cover.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Dove operiamo.&lt;br&gt;&lt;em&gt;Cosa offriamo.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>我们的业务范围。&lt;br&gt;&lt;em&gt;覆盖领域。&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Где мы работаем.&lt;br&gt;&lt;em&gt;Что охватываем.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>حيث نعمل.&lt;br&gt;&lt;em&gt;ما نغطيه.&lt;/em&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="14" ht="16" customHeight="1" s="7">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>s01-title</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Hospitality&lt;br&gt;&amp; Spa</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Hotel&lt;br&gt;&amp; Spa</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>酒店&lt;br&gt;与水疗</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Гостиницы&lt;br&gt;и спа</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>الضيافة&lt;br&gt;والسبا</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15" ht="16" customHeight="1" s="7">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>s01-i1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Hotel &amp; Resort</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Hotel &amp; Resort</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>酒店与度假村</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Отели и курорты</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>فنادق ومنتجعات</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="16" ht="16" customHeight="1" s="7">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>s01-i2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Spa &amp; Wellness</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Spa &amp; Wellness</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>水疗与健康</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Спа и велнес</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>سبا وعافية</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17" ht="16" customHeight="1" s="7">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>s01-i3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>F&amp;B Spaces</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Spazi F&amp;B</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>餐饮空间</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Рестораны и бары</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>مساحات الأغذية</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18" ht="16" customHeight="1" s="7">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>s01-i4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Suite &amp; Guestroom</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Suite &amp; Camere</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>套房与客房</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Сьюты и номера</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>أجنحة وغرف ضيوف</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="19" ht="16" customHeight="1" s="7">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>s01-i5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Lobby &amp; Public Areas</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Lobby &amp; Aree Comuni</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>大堂与公共区域</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Лобби и общие зоны</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>بهو ومناطق عامة</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="20" ht="16" customHeight="1" s="7">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>s02-title</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Residential&lt;br&gt;&amp; Private</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Residenziale</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>住宅&lt;br&gt;与私宅</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Жилой&lt;br&gt;и частный</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>سكني&lt;br&gt;وخاص</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="21" ht="16" customHeight="1" s="7">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>s02-i1</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Villa &amp; Private Home</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Villa &amp; Casa Privata</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>别墅与私宅</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Виллы и частные дома</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>فيلا ومنزل خاص</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="22" ht="16" customHeight="1" s="7">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>s02-i2</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Luxury Apartment</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Appartamento di Lusso</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>豪华公寓</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Люксовые апартаменты</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>شقة فاخرة</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="23" ht="16" customHeight="1" s="7">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>s02-i3</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Penthouse</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Penthouse</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>顶层公寓</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Пентхаус</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>بنتهاوس</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="24" ht="16" customHeight="1" s="7">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>s02-i4</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Interior Fit-out</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Interior Fit-out</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>室内装修</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Отделка интерьера</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>تجهيز الداخلي</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25" ht="16" customHeight="1" s="7">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>s02-i5</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E Supply</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Fornitura FF&amp;E</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E供应</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Поставка FF&amp;E</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>توريد FF&amp;E</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="26" ht="16" customHeight="1" s="7">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>s03-title</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Government&lt;br&gt;Buildings</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Edifici&lt;br&gt;Governativi</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>政府&lt;br&gt;建筑</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Государственные&lt;br&gt;здания</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>المباني&lt;br&gt;الحكومية</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27" ht="16" customHeight="1" s="7">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>s03-i1</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Government Palaces</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Palazzi Governativi</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>政府宫殿</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Правительственные дворцы</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>القصور الحكومية</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="28" ht="16" customHeight="1" s="7">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>s03-i2</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Parliament &amp; Government</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Parlamento &amp; Governo</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>议会与政府</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Парламент и Правительство</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>البرلمان والحكومة</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29" ht="16" customHeight="1" s="7">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>s03-i3</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>State Archives</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Archivio di Stato</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>国家档案馆</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Государственные архивы</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>الأرشيف الوطني</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="30" ht="16" customHeight="1" s="7">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>s03-i4</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Ministerial Offices</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Uffici Ministeriali</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>部委办公室</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Министерские кабинеты</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>مكاتب وزارية</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="31" ht="16" customHeight="1" s="7">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>s03-i5</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Consular &amp; Official Residences</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Residenze Consolari e Ufficiali</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>领事馆与官邸</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Консульские резиденции</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>مقار قنصلية ورسمية</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="32" ht="16" customHeight="1" s="7">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>s03-i6</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Ministries</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Ministeri</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>各部委</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Министерства</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>الوزارات</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="33" ht="16" customHeight="1" s="7">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>s03-i7</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Facades, Ceilings and Flooring</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Facciate, Soffitti e Pavimenti</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>外立面、天花与地板</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Фасады, потолки и полы</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>الواجهات والأسقف والأرضيات</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="34" ht="16" customHeight="1" s="7">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>s04-title</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>零售</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Ритейл</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>تجزئة</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="35" ht="16" customHeight="1" s="7">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>s04-i1</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Flagship Stores</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Flagship Store</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>旗舰店</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Флагманские магазины</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>متاجر رئيسية</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="36" ht="16" customHeight="1" s="7">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>s04-i2</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Pop-up &amp; Brand Activation</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Pop-up &amp; Attivazione Brand</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>快闪店与品牌活动</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Поп-ап и активация бренда</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>متاجر مؤقتة وتفعيل العلامة</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="37" ht="16" customHeight="1" s="7">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>s04-i3</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Shop-in-shop</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Shop-in-shop</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>店中店</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Магазин в магазине</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>متجر داخل متجر</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="38" ht="16" customHeight="1" s="7">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>s04-i4</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Visual Merchandising</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Visual Merchandising</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>视觉陈设</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Визуальный мерчандайзинг</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>تسويق بصري</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="39" ht="16" customHeight="1" s="7">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>s05-title</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Prime Property&lt;br&gt;Sourcing</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Prime Property&lt;br&gt;Sourcing</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>优质房产&lt;br&gt;寻源</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Поиск элитной&lt;br&gt;недвижимости</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>توريد العقارات&lt;br&gt;المتميزة</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="40" ht="16" customHeight="1" s="7">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>s05-i1</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Ultra Prime Residential</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Ultra Prime Residenziale</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>超级优质住宅</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Ультра-премиум жильё</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>سكن فائق التميز</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="41" ht="16" customHeight="1" s="7">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>s05-i2</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Signature Residences</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Signature Residences</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>标志性住所</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Signature Residences</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>مساكن مميزة</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="42" ht="16" customHeight="1" s="7">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>s05-i3</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Bespoke Interiors</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Interni su Misura</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>定制室内设计</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Эксклюзивные интерьеры</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>تصاميم داخلية مخصصة</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="43" ht="16" customHeight="1" s="7">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>s05-i4</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Focus on Milan Italy</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Focus Milano Italia</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>聚焦米兰意大利</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Фокус на Милан</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>التركيز على ميلانو إيطاليا</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="44" ht="16" customHeight="1" s="7">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>s06-title</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Yachting&lt;br&gt;&amp; Marine</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Yachting&lt;br&gt;&amp; Marina</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>游艇&lt;br&gt;与海洋</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Яхтинг&lt;br&gt;и морской</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>يخوت&lt;br&gt;وبحري</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="45" ht="16" customHeight="1" s="7">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>s06-i1</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Superyacht Interior</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Interno Superyacht</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>超级游艇内饰</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Интерьер суперяхты</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>داخلية اليخت الفاخر</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="46" ht="16" customHeight="1" s="7">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>s06-i2</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E Marine-grade</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E per uso marino</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>船用FF&amp;E</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E морского класса</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>FF&amp;E للبيئة البحرية</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="47" ht="16" customHeight="1" s="7">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>s06-i3</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Custom Joinery</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Falegnameria su Misura</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>定制细木工</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Изготовление на заказ</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>نجارة مخصصة</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="48" ht="16" customHeight="1" s="7">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>s06-i4</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Upholstery &amp; Fabric</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Tappezzeria &amp; Tessuti</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>软包与布料</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Обивка и ткани</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>تنجيد وأقمشة</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="49" ht="16" customHeight="1" s="7">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>s07-title</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Digital Layer</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Digital Layer</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>数字化层</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Цифровой слой</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>الطبقة الرقمية</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="50" ht="16" customHeight="1" s="7">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>s07-i1</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Social Media Presence &amp; Strategy</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Social Media Presence &amp; Strategy</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>社交媒体存在与战略</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Присутствие в соцсетях и стратегия</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>الحضور على وسائل التواصل والاستراتيجية</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="51" ht="32" customHeight="1" s="7">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>s07-i2</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Enterprise E-Commerce &amp; Digital Distribution</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Enterprise E-Commerce &amp; Digital Distribution</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>企业电商与数字分销</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Корпоративная электронная коммерция и цифровая дистрибуция</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>التجارة الإلكترونية المؤسسية والتوزيع الرقمي</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="52" ht="32" customHeight="1" s="7">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>s07-i3</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Customer Engagement &amp; Loyalty Programs</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Customer Engagement &amp; Loyalty Programs</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>客户互动与忠诚度计划</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Вовлечённость клиентов и программы лояльности</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>تفاعل العملاء وبرامج الولاء</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="53" ht="32" customHeight="1" s="7">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>s07-i4</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Data &amp; Performance Intelligence</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Data &amp; Performance Intelligence</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>数据与绩效智能</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Аналитика данных и управление эффективностью</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>ذكاء البيانات والأداء</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="54" ht="16" customHeight="1" s="7">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>s07-i5</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Brand Strategy &amp; Creativity</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Brand Strategy &amp; Creativity</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>品牌战略与创意</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Стратегия бренда и креатив</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>استراتيجية العلامة التجارية والإبداع</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="55" ht="16" customHeight="1" s="7">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>s07-i6</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>AI-Powered Process Automation</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>AI-Powered Process Automation</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>AI驱动的流程自动化</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Автоматизация процессов на базе ИИ</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>أتمتة العمليات بالذكاء الاصطناعي</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="56" ht="20" customHeight="1" s="7">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>3 · Il problema</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="57" ht="16" customHeight="1" s="7">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>stag-problem</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>The problem</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Il problema</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>问题所在</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Проблема</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>التحدي</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="58" ht="64" customHeight="1" s="7">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>problem-big</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Great design loses its value&lt;br&gt;the moment it enters&lt;br&gt;&lt;span&gt;an unmanaged supply chain.&lt;/span&gt;</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Un grande design perde valore&lt;br&gt;nel momento in cui entra in&lt;br&gt;&lt;span&gt;una supply chain non presidiata.&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Un eccellente design perde valore&lt;br&gt;&lt;span&gt;con una supply chain non presidiata.&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>再好的设计，一旦进入&lt;br&gt;&lt;span&gt;无人管理的供应链，&lt;/span&gt;&lt;br&gt;便失去价值。</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Великий дизайн теряет ценность&lt;br&gt;попав в&lt;br&gt;&lt;span&gt;неуправляемую цепочку поставок.&lt;/span&gt;</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>يفقد التصميم قيمته&lt;br&gt;فور دخوله&lt;br&gt;&lt;span&gt;سلسلة توريد غير مُدارة.&lt;/span&gt;</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="59" ht="16" customHeight="1" s="7">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>prob-tag1</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Average cost overrun</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Sforamento medio dei costi</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>平均成本超支</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Средний перерасход</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>متوسط تجاوز التكلفة</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="60" ht="64" customHeight="1" s="7">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>prob-txt1</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Hospitality fitouts exceed budget on 7 out of 10 projects, due to poor supplier coordination and uncontrolled change orders.</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>I progetti hospitality sforano il budget in 7 casi su 10, per scarso coordinamento e varianti non controllate.</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>7成酒店装修项目超支，原因是供应商协调不力和变更单失控。</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>7 из 10 проектов превышают бюджет из-за плохой координации поставщиков.</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>7 من أصل 10 مشاريع تتجاوز الميزانية بسبب ضعف التنسيق مع الموردين.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="61" ht="16" customHeight="1" s="7">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>prob-tag2</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Typical delay risk</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Rischio ritardo tipico</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>典型延期风险</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Типичный риск задержки</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>مخاطر التأخير</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="62" ht="64" customHeight="1" s="7">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>prob-txt2</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Without dedicated procurement oversight, interior projects average 4–6 months of slippage — directly eroding pre-opening revenues.</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Senza presidio dedicato, i progetti interior subiscono in media 4–6 mesi di ritardo.</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>缺乏专项采购监督，室内项目平均延期4至6个月，直接侵蚀开业前收益。</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Без надзора проекты задерживаются на 4–6 месяцев.</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>بدون إشراف متخصص، تتأخر المشاريع بمعدل 4-6 أشهر.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="63" ht="16" customHeight="1" s="7">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>prob-tag3</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Information gaps</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Gap informativi</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>信息断层</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Информационные пробелы</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>فجوات المعلومات</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="64" ht="64" customHeight="1" s="7">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>prob-txt3</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Owner, designer and contractor rarely share a single source of truth — creating costly misalignments throughout delivery.</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Committente, designer e appaltatore raramente condividono una sola fonte di verità.</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Committente, progettista e appaltatore raramente condividono un'unica base dati, generando disallineamenti costosi lungo tutto il percorso di realizzazione.</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>业主、设计师和承包商很少共享单一信息源，导致代价高昂的失误。</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Владелец, дизайнер и подрядчик редко используют единый источник данных.</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>نادراً ما يتشارك المالك والمصمم والمقاول مصدراً واحداً للمعلومات.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="65" ht="20" customHeight="1" s="7">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>4 · I numeri</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="66" ht="16" customHeight="1" s="7">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>stag-numbers</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Our supplier network</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>La nostra rete fornitori</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>我们的供应商网络</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Наша сеть поставщиков</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>شبكة موردينا</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="67" ht="32" customHeight="1" s="7">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>num-hl</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Scale, quality&lt;br&gt;and track record&lt;br&gt;&lt;em&gt;by the numbers.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Scala, qualità&lt;br&gt;e track record&lt;br&gt;&lt;em&gt;in numeri.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>规模、品质&lt;br&gt;与业绩&lt;br&gt;&lt;em&gt;数字说话。&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Масштаб, качество&lt;br&gt;и опыт&lt;br&gt;&lt;em&gt;в цифрах.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>الحجم والجودة&lt;br&gt;والسجل الحافل&lt;br&gt;&lt;em&gt;بالأرقام.&lt;/em&gt;</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="68" ht="16" customHeight="1" s="7">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>nc-t1</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Top-tier global clients</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Clienti globali di primo piano</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>全球顶级客户</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Ведущие мировые клиенты</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>عملاء عالميون من الدرجة الأولى</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="69" ht="16" customHeight="1" s="7">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>nc-d1</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Strategic design &amp; supply projects</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Design strategico e fornitura</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>战略设计与供应项目</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>Стратегический дизайн и поставки</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>مشاريع تصميم وتوريد استراتيجية</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="70" ht="16" customHeight="1" s="7">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>nc-t2</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>International awards</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Premi internazionali</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>国际奖项</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Международные награды</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>جوائز دولية</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="71" ht="16" customHeight="1" s="7">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>nc-d2</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Across hospitality, retail &amp; brand</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>In hospitality, retail e brand</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>覆盖酒店、零售与品牌</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>Гостиничный, ритейл и бренды</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>في الضيافة والتجزئة والعلامات</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="72" ht="16" customHeight="1" s="7">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>nc-t3</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Years of experience</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Anni di esperienza</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>年经验</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Лет опыта</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>سنوات خبرة</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="73" ht="16" customHeight="1" s="7">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>nc-d3</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Complex multi-sector projects</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Progetti complessi multi-settore</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>复杂多领域项目</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Сложные многоотраслевые проекты</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>مشاريع متعددة القطاعات</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="74" ht="16" customHeight="1" s="7">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>nc-t4</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Documented savings — floor</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Risparmio documentato — minimo</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>有据可查的节省 — 下限</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Экономия — минимум</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>وفورات موثقة — الحد الأدنى</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="75" ht="16" customHeight="1" s="7">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>nc-d4</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>On a single €6M project</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Su un singolo progetto da €6M</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>单个600万欧元项目</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>На одном проекте €6 млн</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>في مشروع واحد بقيمة 6 مليون يورو</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="76" ht="16" customHeight="1" s="7">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>nc-t5</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Documented savings — ceiling</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Risparmio documentato — massimo</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>有据可查的节省 — 上限</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Экономия — максимум</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>وفورات موثقة — الحد الأعلى</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="77" ht="16" customHeight="1" s="7">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>nc-d5</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>Full-scope engagement</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Coinvolgimento completo</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>全范围介入</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Полный охват работ</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>مشاركة شاملة</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="78" ht="16" customHeight="1" s="7">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>nc-t6</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Average tender savings</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Risparmio medio in gara</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>平均招标节省</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Средняя экономия на тендере</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>متوسط الوفورات في المناقصات</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+    <row r="79" ht="16" customHeight="1" s="7">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>nc-d6</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>On FF&amp;E contract value</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Sul valore contrattuale FF&amp;E</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>按FF&amp;E合同价值</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>От стоимости контракта FF&amp;E</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>على قيمة عقد FF&amp;E</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="80" ht="20" customHeight="1" s="7">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>5 · Perché funziona</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="81" ht="16" customHeight="1" s="7">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>stag-why</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Why it works</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Perché funziona</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>为何有效</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>Почему это работает</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>لماذا ينجح</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="82" ht="16" customHeight="1" s="7">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>wc-t1</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>One single point of contact</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Un solo punto di contatto</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>唯一联络人</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Единая точка контакта</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>نقطة تواصل واحدة</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="83" ht="64" customHeight="1" s="7">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>wc-b1</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Eliminate fragmentation between owner, designer, contractor and supplier. &lt;em&gt;One control point.&lt;/em&gt; Everything converges.</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Elimina la frammentazione tra committente, designer, appaltatore e fornitore. &lt;em&gt;Un punto di controllo.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>消除业主、设计师、承包商与供应商之间的碎片化。&lt;em&gt;一个控制点。&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>Устраните фрагментацию между всеми участниками. &lt;em&gt;Одна точка контроля.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>القضاء على التشتت بين جميع الأطراف. &lt;em&gt;نقطة تحكم واحدة.&lt;/em&gt;</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="84" ht="16" customHeight="1" s="7">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>wc-t2</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>Qualified Italian Suppliers</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Fornitori Italiani Qualificati</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>意大利认证供应商</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>Квалифицированные поставщики</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>موردون إيطاليون مؤهلون</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Italian Suppliers of Excellence</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Fornitori Italiani d'Eccellenza</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>卓越意大利供应商</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Первоклассные итальянские поставщики</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>موردون إيطاليون متميزون</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="80" customHeight="1" s="7">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>wc-b2</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Direct access to a pre-selected panel of Italian manufacturers. &lt;em&gt;Certified quality,&lt;/em&gt; real lead times, no surprises.</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Accesso diretto a un panel di produttori italiani pre-selezionati. &lt;em&gt;Qualità certificata,&lt;/em&gt; lead time reali.</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>直接对接预选意大利制造商名录。&lt;em&gt;品质认证，&lt;/em&gt;真实交货期，无意外。</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>Прямой доступ к итальянским производителям. &lt;em&gt;Сертифицированное качество.&lt;/em&gt;</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>وصول مباشر لقائمة مصنّعين إيطاليين. &lt;em&gt;جودة معتمدة،&lt;/em&gt; مهل حقيقية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Direct access to a panel of partner Italian manufacturers. &lt;em&gt;Certified quality,&lt;/em&gt; guaranteed lead times.</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Accesso diretto a un panel di produttori italiani partners. &lt;em&gt;Qualità certificata,&lt;/em&gt; lead time garantiti.</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>直接对接意大利合作制造商名录。&lt;em&gt;品质认证，&lt;/em&gt;交货期有保障。</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Прямой доступ к панели итальянских производителей-партнёров. &lt;em&gt;Сертифицированное качество,&lt;/em&gt; гарантированные сроки поставки.</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>وصول مباشر لقائمة مصنّعين إيطاليين شركاء. &lt;em&gt;جودة معتمدة،&lt;/em&gt; مهل تسليم مضمونة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1" s="7">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>wc-t3</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>Competitive Tendering</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Gara Competitiva</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>竞争性招标</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>Конкурентные тендеры</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>مناقصات تنافسية</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Highly Competitive Tendering</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Alta competitività di gara</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>高竞争性招标</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Высококонкурентные тендеры</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>مناقصات عالية التنافسية</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="48" customHeight="1" s="7">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>wc-b3</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Structured tenders with like-for-like comparison. &lt;em&gt;Average 8–15% savings&lt;/em&gt; on FF&amp;E contract value.</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Gare strutturate con confronto omogeneo. &lt;em&gt;Risparmio medio 8–15%&lt;/em&gt; sul valore FF&amp;E.</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>结构化招标，同类对比。&lt;em&gt;平均节省8–15%&lt;/em&gt;的FF&amp;E合同价值。</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>Структурированные тендеры. &lt;em&gt;Средняя экономия 8–15%&lt;/em&gt;.</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>مناقصات منظمة بمقارنة متكافئة. &lt;em&gt;توفير متوسط 8–15%&lt;/em&gt;.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Network of subcontractors from the industrial district. &lt;em&gt;Average 8–15% savings&lt;/em&gt; on FF&amp;E value.</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Rete di terzisti del distretto produttivo. &lt;em&gt;Risparmio medio 8–15%&lt;/em&gt; sul valore FF&amp;E.</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>产业集群代工网络。&lt;em&gt;平均节省8–15%&lt;/em&gt;的FF&amp;E价值。</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Сеть субподрядчиков промышленного кластера. &lt;em&gt;Средняя экономия 8–15%&lt;/em&gt; от стоимости FF&amp;E.</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>شبكة من المقاولين من الباطن في المنطقة الصناعية. &lt;em&gt;توفير متوسط 8–15%&lt;/em&gt; من قيمة FF&amp;E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1" s="7">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>wc-t4</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Real-time Budget Control</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>Controllo Budget in Tempo Reale</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>实时预算控制</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>Контроль бюджета в реальном времени</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>رقابة فورية على الميزانية</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="89" ht="96" customHeight="1" s="7">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>wc-b4</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Continuous tracking against approved specifications. &lt;em&gt;No unexpected overrun.&lt;/em&gt; Change orders managed before they become problems.</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Monitoraggio continuo rispetto alle specifiche. &lt;em&gt;Nessuno sforamento imprevisto.&lt;/em&gt;</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Monitoraggio continuo rispetto alle specifiche approvate. &lt;em&gt;Nessuno sforamento imprevisto:&lt;/em&gt; le varianti vengono gestite prima che diventino un problema.</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>对照批准规格持续跟踪。&lt;em&gt;无意外超支。&lt;/em&gt;变更单提前处理。</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Постоянный мониторинг. &lt;em&gt;Никаких неожиданных перерасходов.&lt;/em&gt;</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>متابعة مستمرة. &lt;em&gt;لا تجاوزات مفاجئة.&lt;/em&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Постоянный контроль соответствия утверждённым спецификациям. &lt;em&gt;Никаких неожиданных перерасходов:&lt;/em&gt; изменения устраняются до того, как становятся проблемой.</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>متابعة مستمرة للمطابقة مع المواصفات المعتمدة. &lt;em&gt;لا تجاوزات مفاجئة:&lt;/em&gt; يتم التعامل مع أوامر التغيير قبل أن تتحول إلى مشكلة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1" s="7">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>wc-t5</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Owner's Representative</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Rappresentante del Committente</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Monitoraggio della produzione</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>业主代表</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>Представитель владельца</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
         <is>
           <t>ممثل المالك</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="91" ht="64" customHeight="1" s="7">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>wc-b5</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Your eyes and voice on every site visit and supplier negotiation. &lt;em&gt;Protection of the client's interests&lt;/em&gt; at every stage.</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>I tuoi occhi e la tua voce in ogni visita di cantiere. &lt;em&gt;Tutela degli interessi&lt;/em&gt; del committente.</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Siamo gli occhi del committente in produzione. &lt;em&gt;Verifica della qualità&lt;/em&gt; in ogni fase di progetto.</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>每次现场巡视和供应商谈判中的眼睛与声音。&lt;em&gt;保护客户利益，&lt;/em&gt;贯穿每个阶段。</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>Ваши глаза и голос на каждой встрече. &lt;em&gt;Защита интересов клиента.&lt;/em&gt;</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>عيونك وصوتك في كل زيارة ميدانية. &lt;em&gt;حماية مصالح العميل&lt;/em&gt; في كل مرحلة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Ваши глаза и голос на каждом визите на объект и переговорах с поставщиками. &lt;em&gt;Защита интересов клиента&lt;/em&gt; на каждом этапе.</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>عيونك وصوتك في كل زيارة ميدانية ومفاوضة مع الموردين. &lt;em&gt;حماية مصالح العميل&lt;/em&gt; في كل مرحلة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1" s="7">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>wc-t6</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Integrated Technical Expertise</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Expertise Tecnica Integrata</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>一体化技术专长</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Техническая экспертиза</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>خبرة تقنية متكاملة</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="93" ht="64" customHeight="1" s="7">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>wc-b6</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Drawing package review, MEP coordination, regulatory compliance. &lt;em&gt;What is designed&lt;/em&gt; is what gets built.</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Review disegni, coordinamento MEP, conformità normativa. &lt;em&gt;Quello che viene progettato&lt;/em&gt; è quello che viene costruito.</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>图纸审核、机电协调、法规合规。&lt;em&gt;所设计的，&lt;/em&gt;即所建造的。</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Проверка чертежей, координация MEP. &lt;em&gt;Что спроектировано&lt;/em&gt; — то и построено.</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
         <is>
           <t>مراجعة الرسومات وتنسيق الأنظمة. &lt;em&gt;ما يُصمَّم&lt;/em&gt; هو ما يُبنى.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+    <row r="94" ht="20" customHeight="1" s="7">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>6 · Cosa facciamo</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="95" ht="16" customHeight="1" s="7">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>stag-what</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>What we do</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>Cosa facciamo</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>我们的服务</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>Что мы делаем</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>ما نقدمه</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="96" ht="32" customHeight="1" s="7">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>sol-hl</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>From vision&lt;br&gt;to &lt;em&gt;delivery.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Dalla visione&lt;br&gt;alla &lt;em&gt;consegna.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>从愿景&lt;br&gt;到&lt;em&gt;交付。&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>От концепции&lt;br&gt;до &lt;em&gt;реализации.&lt;/em&gt;</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>من الرؤية&lt;br&gt;إلى &lt;em&gt;التسليم.&lt;/em&gt;</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="97" ht="16" customHeight="1" s="7">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>sol-1</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Turnkey delivery</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Fornitura chiavi in mano</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>交钥匙交付</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Поставка «под ключ»</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>تسليم مفتاح في اليد</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+    <row r="98" ht="16" customHeight="1" s="7">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>sol-2</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Italian supplier aggregation</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Budget Monitoring &amp; Cost Control</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Aggregazione fornitori italiani</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>意大利供应商整合</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>Агрегация итальянских поставщиков</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>تجميع الموردين الإيطاليين</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="99" ht="16" customHeight="1" s="7">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>sol-3</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Supply Chain Management</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>Gestione della Supply Chain</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>供应链管理</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>Управление цепочкой поставок</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>إدارة سلسلة التوريد</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+    <row r="100" ht="16" customHeight="1" s="7">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>sol-4</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E Procurement &amp; Tender</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>Procurement &amp; Gara FF&amp;E</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>FF&amp;E采购与招标</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Закупки и тендер FF&amp;E</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>مشتريات وعطاءات FF&amp;E</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+    <row r="101" ht="32" customHeight="1" s="7">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>sol-5</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Development, Design Refinement, Cost Engineering</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>Sviluppo, Affinamento Progettuale, Cost Engineering</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>开发、设计优化与成本工程</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Разработка, доработка дизайна, инженерия стоимости</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t>التطوير وتحسين التصميم وهندسة التكاليف</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="102" ht="32" customHeight="1" s="7">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>sol-6</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Cost Compliance Design</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>Design a Budget Verificato</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>成本合规设计</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Проектирование с соблюдением бюджета</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>تصميم متوافق مع التكاليف</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="103" ht="20" customHeight="1" s="7">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>7 · Processo</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="104" ht="16" customHeight="1" s="7">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>pr-t1</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Intake &amp; Audit</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>Intake &amp; Audit</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>项目接收与审计</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>Приём и аудит</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>استلام ومراجعة</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Pre-Construction &amp; Audit</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Pre-Construction &amp; Audit</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>施工前审核</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Подготовка и аудит</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>التحضير والتدقيق</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1" s="7">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>pr-i1a</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>Documentation review</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>Analisi documentazione</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>文件审查</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>Анализ документации</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>مراجعة الوثائق</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Drawing &amp; spec review</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Revisione disegni e capitolati</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>图纸与规范审查</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Проверка чертежей и спецификаций</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>مراجعة الرسومات والمواصفات</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1" s="7">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>pr-i1b</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>Budget gap analysis</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Gap analysis budget</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>预算差距分析</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>Анализ бюджетных пробелов</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>تحليل فجوة الميزانية</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Preliminary Budget</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Budget preliminare</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>初步预算</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Предварительный бюджет</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>الميزانية الأولية</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1" s="7">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>pr-i1c</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>Risk mapping</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>Mappatura rischi</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>风险图谱</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>Картирование рисков</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>رسم خريطة المخاطر</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>RFI risk log</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Registro RFI e rischi</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>RFI 风险记录</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Журнал RFI и рисков</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>سجل RFI والمخاطر</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1" s="7">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>pr-i1d</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>Opportunity identification</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>Identificazione opportunità</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>机会识别</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Выявление возможностей</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>تحديد الفرص</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Value engineering</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Value engineering</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>价值工程</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Стоимостной инжиниринг</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>هندسة القيمة</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1" s="7">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>pr-t2</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>Tender &amp; Qualification</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>Gara &amp; Qualifica</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>招标与资质审查</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>Тендер и квалификация</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>مناقصة وتأهيل</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>Bid &amp; Buyout</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Bid &amp; Buyout</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>招标与采购</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Тендер и закупки</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>المناقصة والشراء</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1" s="7">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>pr-i2a</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>Competitive tender</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>Gara competitiva</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>竞争性招标</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>Конкурентный тендер</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>مناقصة تنافسية</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Bid solicitation</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Bando di gara</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Объявление тендера</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>طرح المناقصة</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1" s="7">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>pr-i2b</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Supplier qualification</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Qualifica fornitori</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>供应商资质认证</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>Квалификация поставщиков</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>تأهيل الموردين</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Subcontractor prequalification</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Prequalifica subappaltatori</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>分包商预审</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Предквалификация субподрядчиков</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>التأهيل المسبق للمقاولين من الباطن</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1" s="7">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>pr-i2c</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>Like-for-like comparison</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Confronto omogeneo</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>同类比较</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>Сопоставимое сравнение</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>مقارنة متكافئة</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Bid leveling</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Bid leveling</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>报价比选</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Bid leveling</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>Bid leveling</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1" s="7">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>pr-i2d</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>Panel selection</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>Selezione panel</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>名录筛选</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>Отбор поставщиков</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>اختيار القائمة</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Award recommendation</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Proposta di aggiudicazione</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>授标建议</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>Рекомендация по присуждению</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>توصية الإرساء</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="16" customHeight="1" s="7">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>pr-t3</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>Contract Lock</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Lock Contrattuale</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>合同锁定</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Фиксация контракта</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>إغلاق العقد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Contract Award</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Aggiudicazione</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>合同授予</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>Заключение договора</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>إرساء العقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1" s="7">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>pr-i3a</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>Scope review</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>Review scope</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>范围审查</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>Проверка объёма</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>مراجعة النطاق</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Scope of Work review</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Revisione Scope of Work</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>工作范围审查</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Проверка объёма работ</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>مراجعة نطاق العمل</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1" s="7">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>pr-i3b</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>Milestone triggers</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Milestone triggers</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>里程碑触发机制</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>Триггеры вех</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>محفزات المعالم</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Schedule of Values</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Schedule of Values</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Schedule of Values</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>Schedule of Values</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>Schedule of Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1" s="7">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>pr-i3c</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>Penalty structures</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Strutture di penale</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>罚款结构</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>Штрафные структуры</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>هياكل الغرامات</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Liquidated damages</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Penali contrattuali</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>违约金</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>Неустойка</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>غرامات التأخير</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1" s="7">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>pr-i3d</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Budget tracking</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Budget tracking</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>预算跟踪</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>Отслеживание бюджета</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>تتبع الميزانية</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+    <row r="119" ht="16" customHeight="1" s="7">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>pr-t4</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>Delivery &amp; Site</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>Delivery &amp; Cantiere</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>交付与现场</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>Поставка и объект</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>التسليم والموقع</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
+    <row r="120" ht="16" customHeight="1" s="7">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>pr-i4a</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>Site inspections</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>Ispezioni in loco</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>现场检查</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>Инспекции объекта</t>
         </is>
       </c>
-      <c r="F120" s="7" t="inlineStr">
+      <c r="F120" s="5" t="inlineStr">
         <is>
           <t>عمليات تفتيش الموقع</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="121" ht="16" customHeight="1" s="7">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>pr-i4b</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>Supplier progress</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>Avanzamento fornitori</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>供应商进度</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>Прогресс поставщиков</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>تقدم الموردين</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Progress meetings</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Riunioni di avanzamento</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>进度会议</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>Совещания по ходу работ</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>اجتماعات المتابعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1" s="7">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>pr-i4c</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>Deviation management</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>Gestione deviazioni</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>偏差管理</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>Управление отклонениями</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>إدارة الانحرافات</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Change order log</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Registro varianti</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>变更单记录</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>Журнал изменений</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>سجل أوامر التغيير</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="16" customHeight="1" s="7">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>pr-i4d</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>Escalation protocol</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>Protocollo escalation</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>升级协议</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Протокол эскалации</t>
         </is>
       </c>
-      <c r="F123" s="7" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
         <is>
           <t>بروتوكول التصعيد</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
+    <row r="124" ht="16" customHeight="1" s="7">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>pr-t5</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>Handover &amp; Close-out</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>Consegna &amp; Close-out</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>移交与收尾</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>Сдача и закрытие</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>التسليم والإغلاق</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Closeout &amp; Turnover</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Closeout &amp; Turnover</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>竣工与移交</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>Закрытие и передача</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>الإغلاق والتسليم</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="16" customHeight="1" s="7">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>pr-i5a</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>Acceptance protocol</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>Protocollo di accettazione</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>验收协议</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>Протокол приёмки</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>بروتوكول القبول</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Substantial completion</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Substantial completion</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>实质性竣工</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>Существенное завершение</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>الإنجاز الجوهري</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1" s="7">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>pr-i5b</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>Punch-list</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>Punch-list</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>问题清单</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>Лист замечаний</t>
         </is>
       </c>
-      <c r="F126" s="7" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
         <is>
           <t>قائمة النقاط المعلقة</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+    <row r="127" ht="16" customHeight="1" s="7">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>pr-i5c</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>Final documentation</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>Documentazione finale</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>竣工文档</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>Итоговая документация</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>التوثيق النهائي</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>As-built documentation</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>Documentazione as-built</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>竣工图文件</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>Исполнительная документация</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>مخططات كما نُفِّذت</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1" s="7">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>pr-i5d</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Compliance records</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>Registri di conformità</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>合规记录</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>Записи о соответствии</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>سجلات الامتثال</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Warranty &amp; O&amp;M manuals</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Garanzie e manuali O&amp;M</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>保修与运维手册</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Гарантии и руководства по эксплуатации</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>الضمانات وأدلة التشغيل والصيانة</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1" s="7">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>8 · Profilo / Founder</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
+    <row r="130" ht="16" customHeight="1" s="7">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>stag-who</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>The Founder</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>The Founder</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>创始人</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Основатель</t>
         </is>
       </c>
-      <c r="F130" s="7" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr">
         <is>
           <t>المؤسس</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="131" ht="409.6" customHeight="1" s="7">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>bio</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>Leveraging Brand Experience across diverse sectors: Destination Hospitality, Retail, Brand Activations, Workplaces, and successful premium products in home appliances, sanitary, kitchen, furniture for home, outdoor, public spaces and office environments.&lt;br&gt;&lt;br&gt;Managing projects from strategic design consulting to the complete supply of finished products. Leading teams while overseeing design, strategy, project management, timelines, supplier negotiations, budget control, and analytical tracking of team and project metrics.&lt;br&gt;&lt;br&gt;Strategic design projects for &lt;span class="bio-red"&gt;50+ top-tier global clients&lt;/span&gt; including PepsiCo, 3M, ABB, Unilever, Intel, Amplifon, Adidas, Trenitalia Frecciarossa, Durex, Illy, Cimbali, Ferrarelle, Candy, Hotpoint Ariston, Midea, Vimar, Gewiss, Bosch Rexroth, Uteco, Atlante, Simonelli, Aristarco, Generali, Unipol, Vittoria Assicurazioni, Blue Lagoon Iceland, Salone del Mobile Federlegno Arredo, B&amp;amp;B Italia, Flos, Louis Poulsen, Laufen, Steelcase Coalesse, Viccarbe, Urmet Domus, Dedon, Lema, Moroso, Fendi Casa.&lt;br&gt;&lt;br&gt;&lt;span class="bio-red"&gt;40+&lt;/span&gt; international awards.</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>Esperienza consolidata nel Brand Design su diversi settori: Hospitality di destinazione, Retail, Brand Activation, Workplace e prodotti premium in elettrodomestici, sanitari, cucine, arredamento, outdoor, spazi pubblici e ufficio.&lt;br&gt;&lt;br&gt;Gestione di progetti dalla consulenza strategica di design alla fornitura completa di prodotti finiti. Leadership di team con supervisione di design, strategia, project management, tempi, negoziazione fornitori, controllo budget e analisi delle performance.&lt;br&gt;&lt;br&gt;Progetti di design strategico per &lt;span class="bio-red"&gt;50+ clienti globali di primo piano&lt;/span&gt; tra cui PepsiCo, 3M, ABB, Unilever, Intel, Amplifon, Adidas, Trenitalia Frecciarossa, Durex, Illy, Cimbali, Ferrarelle, Candy, Hotpoint Ariston, Midea, Vimar, Gewiss, Bosch Rexroth, Uteco, Atlante, Simonelli, Aristarco, Generali, Unipol, Vittoria Assicurazioni, Blue Lagoon Iceland, Salone del Mobile Federlegno Arredo, B&amp;amp;B Italia, Flos, Louis Poulsen, Laufen, Steelcase Coalesse, Viccarbe, Urmet Domus, Dedon, Lema, Moroso, Fendi Casa.&lt;br&gt;&lt;br&gt;&lt;span class="bio-red"&gt;40+&lt;/span&gt; premi internazionali.</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>跨多领域积累丰富的品牌体验：目的地酒店、零售、品牌激活、办公空间，以及家电、卫浴、厨房、家具、户外、公共空间等优质产品。&lt;br&gt;&lt;br&gt;项目管理涵盖从战略设计咨询到成品完整供应的全过程。带领团队全面监督设计、战略、项目管理、时间节点、供应商谈判与预算控制。&lt;br&gt;&lt;br&gt;为 &lt;span class="bio-red"&gt;50余位全球顶级客户&lt;/span&gt; 提供战略设计项目，包括百事可乐、3M、ABB、联合利华、英特尔、Amplifon、阿迪达斯、意大利高铁、Durex、Illy、Cimbali、Ferrarelle、Candy、Hotpoint Ariston、Midea、Vimar、Gewiss、Bosch Rexroth、Uteco、Atlante、Simonelli、Aristarco、Generali、Unipol、Vittoria Assicurazioni、冰岛蓝湖、米兰国际家具展、B&amp;amp;B Italia、Flos、Louis Poulsen、Laufen、Steelcase Coalesse、Viccarbe、Urmet Domus、Dedon、Lema、Moroso、Fendi Casa。&lt;br&gt;&lt;br&gt;荣获 &lt;span class="bio-red"&gt;40余项&lt;/span&gt; 国际奖项。</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>Богатый опыт в брендовом дизайне в различных секторах: гостиничный бизнес, ритейл, брендовые активации, рабочие пространства и успешные премиальные продукты в категориях бытовой техники, санузлов, кухонь, мебели, уличных и офисных пространств.&lt;br&gt;&lt;br&gt;Управление проектами от стратегического дизайн-консалтинга до полной поставки готовой продукции. Руководство командами с контролем дизайна, стратегии, управления проектами, сроков, переговоров с поставщиками и бюджета.&lt;br&gt;&lt;br&gt;Стратегические дизайн-проекты для &lt;span class="bio-red"&gt;более 50 ведущих мировых клиентов&lt;/span&gt;, включая PepsiCo, 3M, ABB, Unilever, Intel, Amplifon, Adidas, Trenitalia Frecciarossa, Durex, Illy, Cimbali, Ferrarelle, Candy, Hotpoint Ariston, Midea, Vimar, Gewiss, Bosch Rexroth, Uteco, Atlante, Simonelli, Aristarco, Generali, Unipol, Vittoria Assicurazioni, Blue Lagoon Iceland, Salone del Mobile, B&amp;amp;B Italia, Flos, Louis Poulsen, Laufen, Steelcase Coalesse, Viccarbe, Urmet Domus, Dedon, Lema, Moroso, Fendi Casa.&lt;br&gt;&lt;br&gt;Более &lt;span class="bio-red"&gt;40&lt;/span&gt; международных наград.</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>خبرة واسعة في تصميم العلامات التجارية عبر قطاعات متعددة: ضيافة الوجهات، التجزئة، تفعيل العلامات التجارية، بيئات العمل والمنتجات المميزة في الأجهزة المنزلية والصحية والمطابخ والأثاث والمساحات الخارجية والعامة والمكتبية.&lt;br&gt;&lt;br&gt;إدارة مشاريع تمتد من الاستشارات الاستراتيجية للتصميم إلى التوريد الكامل للمنتجات النهائية، مع قيادة الفرق والإشراف على التصميم والاستراتيجية وإدارة المشاريع والمواعيد والتفاوض مع الموردين والميزانية.&lt;br&gt;&lt;br&gt;مشاريع تصميم استراتيجية لأكثر من &lt;span class="bio-red"&gt;50 عميلاً عالمياً من الدرجة الأولى&lt;/span&gt; بما في ذلك PepsiCo و3M وABB وUnilever وIntel وAmplifon وAdidas وTrenitalia Frecciarossa وDurex وIlly وCimbali وFerrarelle وCandy وHotpoint Ariston وMidea وVimar وGewiss وBosch Rexroth وAtlante وSimonelli وAristarco وGenerali وUnipol وVittoria Assicurazioni وBlue Lagoon Iceland وSalone del Mobile وB&amp;amp;B Italia وFlos وLouis Poulsen وLaufen وSteelcase Coalesse وViccarbe وUrmet Domus وDedon وLema وMoreso وFendi Casa.&lt;br&gt;&lt;br&gt;أكثر من &lt;span class="bio-red"&gt;40&lt;/span&gt; جائزة دولية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Esperienza consolidata di Brand Experience Design in svariati settori: Hospitality Destinations, Retail, Brand Activation, Workplace, oltre al Design di prodotti premium come elettrodomestici, sanitari, cucine, arredamento, outdoor, spazi pubblici e ufficio.&lt;br&gt;&lt;br&gt;Gestione di progetti dalla consulenza strategica di design alla fornitura completa di prodotti finiti. Leadership di team con supervisione di design, strategia, project management, tempi, negoziazione fornitori, controllo budget e analisi delle performance.&lt;br&gt;&lt;br&gt;Progetti di design strategico per &lt;span class="bio-red"&gt;50+ clienti globali di primo piano&lt;/span&gt; tra cui PepsiCo, 3M, ABB, Unilever, Intel, Amplifon, Adidas, Trenitalia Frecciarossa, Durex, Illy, Cimbali, Ferrarelle, Candy, Hotpoint Ariston, Midea, Vimar, Gewiss, Bosch Rexroth, Uteco, Atlante, Simonelli, Aristarco, Generali, Unipol, Vittoria Assicurazioni, Blue Lagoon Iceland, Salone del Mobile Federlegno Arredo, B&amp;amp;B Italia, Flos, Louis Poulsen, Laufen, Steelcase Coalesse, Viccarbe, Urmet Domus, Dedon, Lema, Moroso, Fendi Casa.&lt;br&gt;&lt;br&gt;&lt;span class="bio-red"&gt;40+&lt;/span&gt; premi internazionali.</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>凭借跨领域的品牌体验设计实力，业务涵盖目的地度假酒店、零售、品牌活化与办公空间，并成功打造家电、卫浴、厨房、家具、户外及办公环境等高端产品线。&lt;br&gt;&lt;br&gt;项目管理涵盖从战略设计咨询到成品全案供应的完整流程，带领团队统筹设计、战略、项目管理、时间节点、供应商谈判与预算控制，并对团队及项目绩效指标进行量化追踪。&lt;br&gt;&lt;br&gt;为 &lt;span class="bio-red"&gt;50余家全球顶级客户&lt;/span&gt; 提供战略设计项目，包括百事可乐、3M、ABB、联合利华、英特尔、Amplifon、阿迪达斯、意大利高铁、Durex、Illy、Cimbali、Ferrarelle、Candy、Hotpoint Ariston、Midea、Vimar、Gewiss、Bosch Rexroth、Uteco、Atlante、Simonelli、Aristarco、Generali、Unipol、Vittoria Assicurazioni、冰岛蓝湖、米兰国际家具展、B&amp;amp;B Italia、Flos、Louis Poulsen、Laufen、Steelcase Coalesse、Viccarbe、Urmet Domus、Dedon、Lema、Moroso、Fendi Casa。&lt;br&gt;&lt;br&gt;荣获 &lt;span class="bio-red"&gt;40余项&lt;/span&gt; 国际奖项。</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Многолетний опыт в области бренд-дизайна в самых разных секторах: гостиничная индустрия для туристических направлений, ритейл, брендовые активации, рабочие пространства, а также успешные премиальные продукты в категориях бытовой техники, сантехники, кухонь, мебели для дома, уличных, общественных и офисных пространств.&lt;br&gt;&lt;br&gt;Управление проектами — от стратегического дизайн-консалтинга до полной поставки готовой продукции. Руководство командами с контролем дизайна, стратегии, управления проектами, сроков, переговоров с поставщиками и бюджета, а также аналитическим отслеживанием показателей команды и проекта.&lt;br&gt;&lt;br&gt;Стратегические дизайн-проекты для более чем &lt;span class="bio-red"&gt;50 ведущих мировых клиентов&lt;/span&gt;, включая PepsiCo, 3M, ABB, Unilever, Intel, Amplifon, Adidas, Trenitalia Frecciarossa, Durex, Illy, Cimbali, Ferrarelle, Candy, Hotpoint Ariston, Midea, Vimar, Gewiss, Bosch Rexroth, Uteco, Atlante, Simonelli, Aristarco, Generali, Unipol, Vittoria Assicurazioni, Blue Lagoon Iceland, Salone del Mobile Federlegno Arredo, B&amp;amp;B Italia, Flos, Louis Poulsen, Laufen, Steelcase Coalesse, Viccarbe, Urmet Domus, Dedon, Lema, Moroso, Fendi Casa.&lt;br&gt;&lt;br&gt;Более &lt;span class="bio-red"&gt;40&lt;/span&gt; международных наград.</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>خبرة راسخة في تصميم تجربة العلامة التجارية عبر قطاعات متنوعة: ضيافة الوجهات السياحية، التجزئة، تفعيل العلامات التجارية، بيئات العمل، إضافة إلى منتجات مميزة وناجحة في مجالات الأجهزة المنزلية والصحية والمطابخ والأثاث المنزلي والخارجي والمساحات العامة والمكتبية.&lt;br&gt;&lt;br&gt;إدارة مشاريع تمتد من الاستشارات الاستراتيجية للتصميم إلى التوريد الكامل للمنتجات النهائية. قيادة فرق العمل مع الإشراف على التصميم والاستراتيجية وإدارة المشاريع والمواعيد والتفاوض مع الموردين والتحكم في الميزانية، إلى جانب المتابعة التحليلية لمؤشرات أداء الفريق والمشروع.&lt;br&gt;&lt;br&gt;مشاريع تصميم استراتيجية لأكثر من &lt;span class="bio-red"&gt;50 عميلاً عالمياً من الدرجة الأولى&lt;/span&gt;، بما في ذلك PepsiCo و3M وABB وUnilever وIntel وAmplifon وAdidas وTrenitalia Frecciarossa وDurex وIlly وCimbali وFerrarelle وCandy وHotpoint Ariston وMidea وVimar وGewiss وBosch Rexroth وUteco وAtlante وSimonelli وAristarco وGenerali وUnipol وVittoria Assicurazioni وBlue Lagoon Iceland وSalone del Mobile Federlegno Arredo وB&amp;amp;B Italia وFlos وLouis Poulsen وLaufen وSteelcase Coalesse وViccarbe وUrmet Domus وDedon وLema وMoroso وFendi Casa.&lt;br&gt;&lt;br&gt;أكثر من &lt;span class="bio-red"&gt;40&lt;/span&gt; جائزة دولية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1" s="7">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>stag-clients</t>
         </is>
       </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>客户案例</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>Портфолио</t>
         </is>
       </c>
-      <c r="F132" s="7" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr">
         <is>
           <t>المحفظة</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="133" ht="16" customHeight="1" s="7">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>clients-btn</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>Access Reserved</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>Accesso Riservato</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>进入专属区域</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>Закрытая зона</t>
         </is>
       </c>
-      <c r="F133" s="7" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>الوصول المحجوز</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+    <row r="134" ht="20" customHeight="1" s="7">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>9 · Chiusura (CTA)</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="135" ht="16" customHeight="1" s="7">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>cta-hl-1</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>Every space.</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>Every space.</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>每一个空间。</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>Каждое пространство.</t>
         </is>
       </c>
-      <c r="F135" s="7" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
         <is>
           <t>كلّ فضاء،</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+    <row r="136" ht="16" customHeight="1" s="7">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>cta-hl-2</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>Delivered.</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>Delivered.</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>完美交付。</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>Реализовано.</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
         <is>
           <t>مُنجَز.</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+    <row r="137" ht="16" customHeight="1" s="7">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>cta-sub</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>Worldwide Projects</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>Worldwide Projects</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>全球项目</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t>Международные проекты</t>
         </is>
       </c>
-      <c r="F137" s="7" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
         <is>
           <t>مشاريع عالمية</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+    <row r="138" ht="20" customHeight="1" s="7">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Area riservata (finestra password)</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="139" ht="16" customHeight="1" s="7">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>pwd-title</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>Reserved Area</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>Area Riservata</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>专属区域</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>Закрытый раздел</t>
         </is>
       </c>
-      <c r="F139" s="7" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>المنطقة المحجوزة</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+    <row r="140" ht="16" customHeight="1" s="7">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>pwd-placeholder</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Enter password</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>Inserisci la password</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>请输入密码</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Введите пароль</t>
         </is>
       </c>
-      <c r="F140" s="7" t="inlineStr">
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>أدخل كلمة المرور</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="141" ht="16" customHeight="1" s="7">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>pwd-submit</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>Enter</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>Entra</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>进入</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="4" t="inlineStr">
         <is>
           <t>Войти</t>
         </is>
       </c>
-      <c r="F141" s="7" t="inlineStr">
+      <c r="F141" s="5" t="inlineStr">
         <is>
           <t>دخول</t>
         </is>
@@ -4703,8 +4719,8 @@
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A134:F134"/>
@@ -4714,5 +4730,6 @@
     <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/_review/Potential_Revisione_Traduzioni.xlsx
+++ b/_review/Potential_Revisione_Traduzioni.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <family val="2"/>
       <color rgb="FF999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E7D32"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -128,6 +133,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3579,27 +3590,27 @@
           <t>pr-t1</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>Pre-Construction &amp; Audit</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>Pre-Construction &amp; Audit</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D104" s="11" t="inlineStr">
         <is>
           <t>施工前审核</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="E104" s="11" t="inlineStr">
         <is>
           <t>Подготовка и аудит</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
+      <c r="F104" s="12" t="inlineStr">
         <is>
           <t>التحضير والتدقيق</t>
         </is>
@@ -3611,27 +3622,27 @@
           <t>pr-i1a</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>Drawing &amp; spec review</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>Revisione disegni e capitolati</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
+      <c r="D105" s="11" t="inlineStr">
         <is>
           <t>图纸与规范审查</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>Проверка чертежей и спецификаций</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
         <is>
           <t>مراجعة الرسومات والمواصفات</t>
         </is>
@@ -3675,27 +3686,27 @@
           <t>pr-i1c</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>RFI risk log</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
         <is>
           <t>Registro RFI e rischi</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="D107" s="11" t="inlineStr">
         <is>
           <t>RFI 风险记录</t>
         </is>
       </c>
-      <c r="E107" s="9" t="inlineStr">
+      <c r="E107" s="11" t="inlineStr">
         <is>
           <t>Журнал RFI и рисков</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr">
         <is>
           <t>سجل RFI والمخاطر</t>
         </is>
@@ -3707,27 +3718,27 @@
           <t>pr-i1d</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>Value engineering</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C108" s="11" t="inlineStr">
         <is>
           <t>Value engineering</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D108" s="11" t="inlineStr">
         <is>
           <t>价值工程</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="E108" s="11" t="inlineStr">
         <is>
           <t>Стоимостной инжиниринг</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr">
+      <c r="F108" s="12" t="inlineStr">
         <is>
           <t>هندسة القيمة</t>
         </is>
@@ -3739,27 +3750,27 @@
           <t>pr-t2</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>Bid &amp; Buyout</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>Bid &amp; Buyout</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D109" s="11" t="inlineStr">
         <is>
           <t>招标与采购</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="E109" s="11" t="inlineStr">
         <is>
           <t>Тендер и закупки</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F109" s="12" t="inlineStr">
         <is>
           <t>المناقصة والشراء</t>
         </is>
@@ -3771,27 +3782,27 @@
           <t>pr-i2a</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>Bid solicitation</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>Bando di gara</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D110" s="11" t="inlineStr">
         <is>
           <t>招标公告</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E110" s="11" t="inlineStr">
         <is>
           <t>Объявление тендера</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
         <is>
           <t>طرح المناقصة</t>
         </is>
@@ -3803,27 +3814,27 @@
           <t>pr-i2b</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>Subcontractor prequalification</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>Prequalifica subappaltatori</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D111" s="11" t="inlineStr">
         <is>
           <t>分包商预审</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E111" s="11" t="inlineStr">
         <is>
           <t>Предквалификация субподрядчиков</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="12" t="inlineStr">
         <is>
           <t>التأهيل المسبق للمقاولين من الباطن</t>
         </is>
@@ -3835,27 +3846,27 @@
           <t>pr-i2c</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="D112" s="11" t="inlineStr">
         <is>
           <t>报价比选</t>
         </is>
       </c>
-      <c r="E112" s="9" t="inlineStr">
+      <c r="E112" s="11" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="12" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
@@ -3867,27 +3878,27 @@
           <t>pr-i2d</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>Award recommendation</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>Proposta di aggiudicazione</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>授标建议</t>
         </is>
       </c>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="E113" s="11" t="inlineStr">
         <is>
           <t>Рекомендация по присуждению</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="12" t="inlineStr">
         <is>
           <t>توصية الإرساء</t>
         </is>
@@ -3899,27 +3910,27 @@
           <t>pr-t3</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>Contract Award</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>Aggiudicazione</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
+      <c r="D114" s="11" t="inlineStr">
         <is>
           <t>合同授予</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="E114" s="11" t="inlineStr">
         <is>
           <t>Заключение договора</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="12" t="inlineStr">
         <is>
           <t>إرساء العقد</t>
         </is>
@@ -3931,27 +3942,27 @@
           <t>pr-i3a</t>
         </is>
       </c>
-      <c r="B115" s="9" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>Scope of Work review</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>Revisione Scope of Work</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>工作范围审查</t>
         </is>
       </c>
-      <c r="E115" s="9" t="inlineStr">
+      <c r="E115" s="11" t="inlineStr">
         <is>
           <t>Проверка объёма работ</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
+      <c r="F115" s="12" t="inlineStr">
         <is>
           <t>مراجعة نطاق العمل</t>
         </is>
@@ -3963,27 +3974,27 @@
           <t>pr-i3b</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
+      <c r="D116" s="11" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="E116" s="11" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="12" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
@@ -3995,27 +4006,27 @@
           <t>pr-i3c</t>
         </is>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>Liquidated damages</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr">
         <is>
           <t>Penali contrattuali</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D117" s="11" t="inlineStr">
         <is>
           <t>违约金</t>
         </is>
       </c>
-      <c r="E117" s="9" t="inlineStr">
+      <c r="E117" s="11" t="inlineStr">
         <is>
           <t>Неустойка</t>
         </is>
       </c>
-      <c r="F117" s="10" t="inlineStr">
+      <c r="F117" s="12" t="inlineStr">
         <is>
           <t>غرامات التأخير</t>
         </is>
@@ -4123,27 +4134,27 @@
           <t>pr-i4b</t>
         </is>
       </c>
-      <c r="B121" s="9" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>Progress meetings</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="C121" s="11" t="inlineStr">
         <is>
           <t>Riunioni di avanzamento</t>
         </is>
       </c>
-      <c r="D121" s="9" t="inlineStr">
+      <c r="D121" s="11" t="inlineStr">
         <is>
           <t>进度会议</t>
         </is>
       </c>
-      <c r="E121" s="9" t="inlineStr">
+      <c r="E121" s="11" t="inlineStr">
         <is>
           <t>Совещания по ходу работ</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="12" t="inlineStr">
         <is>
           <t>اجتماعات المتابعة</t>
         </is>
@@ -4155,27 +4166,27 @@
           <t>pr-i4c</t>
         </is>
       </c>
-      <c r="B122" s="9" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>Change order log</t>
         </is>
       </c>
-      <c r="C122" s="9" t="inlineStr">
+      <c r="C122" s="11" t="inlineStr">
         <is>
           <t>Registro varianti</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr">
+      <c r="D122" s="11" t="inlineStr">
         <is>
           <t>变更单记录</t>
         </is>
       </c>
-      <c r="E122" s="9" t="inlineStr">
+      <c r="E122" s="11" t="inlineStr">
         <is>
           <t>Журнал изменений</t>
         </is>
       </c>
-      <c r="F122" s="10" t="inlineStr">
+      <c r="F122" s="12" t="inlineStr">
         <is>
           <t>سجل أوامر التغيير</t>
         </is>
@@ -4219,27 +4230,27 @@
           <t>pr-t5</t>
         </is>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>Closeout &amp; Turnover</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
         <is>
           <t>Closeout &amp; Turnover</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr">
+      <c r="D124" s="11" t="inlineStr">
         <is>
           <t>竣工与移交</t>
         </is>
       </c>
-      <c r="E124" s="9" t="inlineStr">
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>Закрытие и передача</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="12" t="inlineStr">
         <is>
           <t>الإغلاق والتسليم</t>
         </is>
@@ -4251,27 +4262,27 @@
           <t>pr-i5a</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>Substantial completion</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C125" s="11" t="inlineStr">
         <is>
           <t>Substantial completion</t>
         </is>
       </c>
-      <c r="D125" s="9" t="inlineStr">
+      <c r="D125" s="11" t="inlineStr">
         <is>
           <t>实质性竣工</t>
         </is>
       </c>
-      <c r="E125" s="9" t="inlineStr">
+      <c r="E125" s="11" t="inlineStr">
         <is>
           <t>Существенное завершение</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="12" t="inlineStr">
         <is>
           <t>الإنجاز الجوهري</t>
         </is>
@@ -4315,27 +4326,27 @@
           <t>pr-i5c</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>As-built documentation</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C127" s="11" t="inlineStr">
         <is>
           <t>Documentazione as-built</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D127" s="11" t="inlineStr">
         <is>
           <t>竣工图文件</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E127" s="11" t="inlineStr">
         <is>
           <t>Исполнительная документация</t>
         </is>
       </c>
-      <c r="F127" s="10" t="inlineStr">
+      <c r="F127" s="12" t="inlineStr">
         <is>
           <t>مخططات كما نُفِّذت</t>
         </is>
@@ -4347,27 +4358,27 @@
           <t>pr-i5d</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>Warranty &amp; O&amp;M manuals</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C128" s="11" t="inlineStr">
         <is>
           <t>Garanzie e manuali O&amp;M</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D128" s="11" t="inlineStr">
         <is>
           <t>保修与运维手册</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E128" s="11" t="inlineStr">
         <is>
           <t>Гарантии и руководства по эксплуатации</t>
         </is>
       </c>
-      <c r="F128" s="10" t="inlineStr">
+      <c r="F128" s="12" t="inlineStr">
         <is>
           <t>الضمانات وأدلة التشغيل والصيانة</t>
         </is>
@@ -4719,8 +4730,8 @@
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A134:F134"/>

--- a/_review/Potential_Revisione_Traduzioni.xlsx
+++ b/_review/Potential_Revisione_Traduzioni.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traduzioni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numeri" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,9 +53,35 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri (Corpo)"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFC00000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00999999"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001E7D32"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -76,11 +103,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C4"/>
+        <fgColor rgb="00C71617"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -103,11 +130,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -122,6 +163,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -129,17 +179,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,12 +558,12 @@
   <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="7" min="1" max="1"/>
-    <col width="34" customWidth="1" style="7" min="2" max="6"/>
+    <col width="16" customWidth="1" style="10" min="1" max="1"/>
+    <col width="34" customWidth="1" style="10" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="34" customHeight="1" s="10">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Potential — Revisione traduzioni  ·  Modifica le celle di lingua (non la colonna ID). Le righe rosse sono i titoli di sezione (ordine del sito). Simboli &lt;br&gt;/&lt;em&gt; = a capo/evidenziazioni, lasciarli.</t>
         </is>
@@ -552,14 +601,14 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" s="7">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3" ht="20" customHeight="1" s="10">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Elementi ricorrenti (scroll, footer)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="7">
+    <row r="4" ht="16" customHeight="1" s="10">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>scroll-down</t>
@@ -591,7 +640,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="7">
+    <row r="5" ht="16" customHeight="1" s="10">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>footer-copy</t>
@@ -623,7 +672,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="7">
+    <row r="6" ht="16" customHeight="1" s="10">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>footer-privacy</t>
@@ -655,14 +704,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="10">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>1 · Frase d'apertura</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="7">
+    <row r="8" ht="16" customHeight="1" s="10">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>intro-hl-1</t>
@@ -694,7 +743,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="7">
+    <row r="9" ht="16" customHeight="1" s="10">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>intro-hl-2</t>
@@ -726,7 +775,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="7">
+    <row r="10" ht="16" customHeight="1" s="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>intro-hl-3</t>
@@ -758,14 +807,14 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="7">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="10">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>2 · Aree di competenza</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" s="7">
+    <row r="12" ht="16" customHeight="1" s="10">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>stag-coverage</t>
@@ -797,7 +846,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1" s="7">
+    <row r="13" ht="32" customHeight="1" s="10">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>sectors-hl</t>
@@ -829,7 +878,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" s="7">
+    <row r="14" ht="16" customHeight="1" s="10">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>s01-title</t>
@@ -861,7 +910,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" s="7">
+    <row r="15" ht="16" customHeight="1" s="10">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>s01-i1</t>
@@ -893,7 +942,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="7">
+    <row r="16" ht="16" customHeight="1" s="10">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>s01-i2</t>
@@ -925,7 +974,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" s="7">
+    <row r="17" ht="16" customHeight="1" s="10">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>s01-i3</t>
@@ -957,7 +1006,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="7">
+    <row r="18" ht="16" customHeight="1" s="10">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>s01-i4</t>
@@ -989,7 +1038,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" s="7">
+    <row r="19" ht="16" customHeight="1" s="10">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>s01-i5</t>
@@ -1021,7 +1070,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="7">
+    <row r="20" ht="16" customHeight="1" s="10">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>s02-title</t>
@@ -1053,7 +1102,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" s="7">
+    <row r="21" ht="16" customHeight="1" s="10">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>s02-i1</t>
@@ -1085,7 +1134,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1" s="7">
+    <row r="22" ht="16" customHeight="1" s="10">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>s02-i2</t>
@@ -1117,7 +1166,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" s="7">
+    <row r="23" ht="16" customHeight="1" s="10">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>s02-i3</t>
@@ -1149,7 +1198,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" s="7">
+    <row r="24" ht="16" customHeight="1" s="10">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>s02-i4</t>
@@ -1181,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" s="7">
+    <row r="25" ht="16" customHeight="1" s="10">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>s02-i5</t>
@@ -1213,7 +1262,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" s="7">
+    <row r="26" ht="16" customHeight="1" s="10">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>s03-title</t>
@@ -1245,7 +1294,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1" s="7">
+    <row r="27" ht="16" customHeight="1" s="10">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>s03-i1</t>
@@ -1277,7 +1326,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1" s="7">
+    <row r="28" ht="16" customHeight="1" s="10">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>s03-i2</t>
@@ -1309,7 +1358,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1" s="7">
+    <row r="29" ht="16" customHeight="1" s="10">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>s03-i3</t>
@@ -1341,7 +1390,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="7">
+    <row r="30" ht="16" customHeight="1" s="10">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>s03-i4</t>
@@ -1373,7 +1422,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" s="7">
+    <row r="31" ht="16" customHeight="1" s="10">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>s03-i5</t>
@@ -1405,7 +1454,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1" s="7">
+    <row r="32" ht="16" customHeight="1" s="10">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>s03-i6</t>
@@ -1437,7 +1486,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" s="7">
+    <row r="33" ht="16" customHeight="1" s="10">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>s03-i7</t>
@@ -1469,7 +1518,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" s="7">
+    <row r="34" ht="16" customHeight="1" s="10">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>s04-title</t>
@@ -1501,7 +1550,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1" s="7">
+    <row r="35" ht="16" customHeight="1" s="10">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>s04-i1</t>
@@ -1533,7 +1582,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1" s="7">
+    <row r="36" ht="16" customHeight="1" s="10">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>s04-i2</t>
@@ -1565,7 +1614,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1" s="7">
+    <row r="37" ht="16" customHeight="1" s="10">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>s04-i3</t>
@@ -1597,7 +1646,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1" s="7">
+    <row r="38" ht="16" customHeight="1" s="10">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>s04-i4</t>
@@ -1629,7 +1678,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1" s="7">
+    <row r="39" ht="16" customHeight="1" s="10">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>s05-title</t>
@@ -1661,7 +1710,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" s="7">
+    <row r="40" ht="16" customHeight="1" s="10">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>s05-i1</t>
@@ -1693,7 +1742,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" s="7">
+    <row r="41" ht="16" customHeight="1" s="10">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>s05-i2</t>
@@ -1725,7 +1774,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1" s="7">
+    <row r="42" ht="16" customHeight="1" s="10">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>s05-i3</t>
@@ -1757,7 +1806,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1" s="7">
+    <row r="43" ht="16" customHeight="1" s="10">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>s05-i4</t>
@@ -1789,7 +1838,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1" s="7">
+    <row r="44" ht="16" customHeight="1" s="10">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>s06-title</t>
@@ -1821,7 +1870,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1" s="7">
+    <row r="45" ht="16" customHeight="1" s="10">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>s06-i1</t>
@@ -1853,7 +1902,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1" s="7">
+    <row r="46" ht="16" customHeight="1" s="10">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>s06-i2</t>
@@ -1885,7 +1934,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1" s="7">
+    <row r="47" ht="16" customHeight="1" s="10">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>s06-i3</t>
@@ -1917,7 +1966,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1" s="7">
+    <row r="48" ht="16" customHeight="1" s="10">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>s06-i4</t>
@@ -1949,7 +1998,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1" s="7">
+    <row r="49" ht="16" customHeight="1" s="10">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>s07-title</t>
@@ -1981,7 +2030,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1" s="7">
+    <row r="50" ht="16" customHeight="1" s="10">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>s07-i1</t>
@@ -2013,7 +2062,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1" s="7">
+    <row r="51" ht="32" customHeight="1" s="10">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>s07-i2</t>
@@ -2045,7 +2094,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="32" customHeight="1" s="7">
+    <row r="52" ht="32" customHeight="1" s="10">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>s07-i3</t>
@@ -2077,7 +2126,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1" s="7">
+    <row r="53" ht="32" customHeight="1" s="10">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>s07-i4</t>
@@ -2109,7 +2158,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1" s="7">
+    <row r="54" ht="16" customHeight="1" s="10">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>s07-i5</t>
@@ -2141,7 +2190,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1" s="7">
+    <row r="55" ht="16" customHeight="1" s="10">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>s07-i6</t>
@@ -2173,14 +2222,14 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1" s="7">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="56" ht="20" customHeight="1" s="10">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>3 · Il problema</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1" s="7">
+    <row r="57" ht="16" customHeight="1" s="10">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>stag-problem</t>
@@ -2212,7 +2261,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="64" customHeight="1" s="7">
+    <row r="58" ht="64" customHeight="1" s="10">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>problem-big</t>
@@ -2244,7 +2293,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1" s="7">
+    <row r="59" ht="16" customHeight="1" s="10">
       <c r="A59" s="3" t="inlineStr">
         <is>
           <t>prob-tag1</t>
@@ -2276,7 +2325,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="64" customHeight="1" s="7">
+    <row r="60" ht="64" customHeight="1" s="10">
       <c r="A60" s="3" t="inlineStr">
         <is>
           <t>prob-txt1</t>
@@ -2308,7 +2357,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1" s="7">
+    <row r="61" ht="16" customHeight="1" s="10">
       <c r="A61" s="3" t="inlineStr">
         <is>
           <t>prob-tag2</t>
@@ -2340,7 +2389,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="64" customHeight="1" s="7">
+    <row r="62" ht="64" customHeight="1" s="10">
       <c r="A62" s="3" t="inlineStr">
         <is>
           <t>prob-txt2</t>
@@ -2372,7 +2421,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1" s="7">
+    <row r="63" ht="16" customHeight="1" s="10">
       <c r="A63" s="3" t="inlineStr">
         <is>
           <t>prob-tag3</t>
@@ -2404,7 +2453,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="64" customHeight="1" s="7">
+    <row r="64" ht="64" customHeight="1" s="10">
       <c r="A64" s="3" t="inlineStr">
         <is>
           <t>prob-txt3</t>
@@ -2436,14 +2485,14 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1" s="7">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="65" ht="20" customHeight="1" s="10">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>4 · I numeri</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1" s="7">
+    <row r="66" ht="16" customHeight="1" s="10">
       <c r="A66" s="3" t="inlineStr">
         <is>
           <t>stag-numbers</t>
@@ -2454,9 +2503,9 @@
           <t>Our supplier network</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>La nostra rete fornitori</t>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>I nostri numeri</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2475,7 +2524,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="32" customHeight="1" s="7">
+    <row r="67" ht="32" customHeight="1" s="10">
       <c r="A67" s="3" t="inlineStr">
         <is>
           <t>num-hl</t>
@@ -2507,7 +2556,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1" s="7">
+    <row r="68" ht="16" customHeight="1" s="10">
       <c r="A68" s="3" t="inlineStr">
         <is>
           <t>nc-t1</t>
@@ -2539,7 +2588,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1" s="7">
+    <row r="69" ht="16" customHeight="1" s="10">
       <c r="A69" s="3" t="inlineStr">
         <is>
           <t>nc-d1</t>
@@ -2571,7 +2620,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1" s="7">
+    <row r="70" ht="16" customHeight="1" s="10">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>nc-t2</t>
@@ -2603,7 +2652,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1" s="7">
+    <row r="71" ht="16" customHeight="1" s="10">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>nc-d2</t>
@@ -2635,7 +2684,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1" s="7">
+    <row r="72" ht="16" customHeight="1" s="10">
       <c r="A72" s="3" t="inlineStr">
         <is>
           <t>nc-t3</t>
@@ -2667,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1" s="7">
+    <row r="73" ht="16" customHeight="1" s="10">
       <c r="A73" s="3" t="inlineStr">
         <is>
           <t>nc-d3</t>
@@ -2699,7 +2748,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1" s="7">
+    <row r="74" ht="16" customHeight="1" s="10">
       <c r="A74" s="3" t="inlineStr">
         <is>
           <t>nc-t4</t>
@@ -2731,7 +2780,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1" s="7">
+    <row r="75" ht="16" customHeight="1" s="10">
       <c r="A75" s="3" t="inlineStr">
         <is>
           <t>nc-d4</t>
@@ -2763,7 +2812,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1" s="7">
+    <row r="76" ht="16" customHeight="1" s="10">
       <c r="A76" s="3" t="inlineStr">
         <is>
           <t>nc-t5</t>
@@ -2795,7 +2844,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1" s="7">
+    <row r="77" ht="16" customHeight="1" s="10">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>nc-d5</t>
@@ -2827,7 +2876,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1" s="7">
+    <row r="78" ht="16" customHeight="1" s="10">
       <c r="A78" s="3" t="inlineStr">
         <is>
           <t>nc-t6</t>
@@ -2859,7 +2908,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1" s="7">
+    <row r="79" ht="16" customHeight="1" s="10">
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>nc-d6</t>
@@ -2891,14 +2940,14 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1" s="7">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="80" ht="20" customHeight="1" s="10">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>5 · Perché funziona</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1" s="7">
+    <row r="81" ht="16" customHeight="1" s="10">
       <c r="A81" s="3" t="inlineStr">
         <is>
           <t>stag-why</t>
@@ -2930,7 +2979,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1" s="7">
+    <row r="82" ht="16" customHeight="1" s="10">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>wc-t1</t>
@@ -2962,7 +3011,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="64" customHeight="1" s="7">
+    <row r="83" ht="64" customHeight="1" s="10">
       <c r="A83" s="3" t="inlineStr">
         <is>
           <t>wc-b1</t>
@@ -2994,7 +3043,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="16" customHeight="1" s="7">
+    <row r="84" ht="16" customHeight="1" s="10">
       <c r="A84" s="3" t="inlineStr">
         <is>
           <t>wc-t2</t>
@@ -3026,7 +3075,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="80" customHeight="1" s="7">
+    <row r="85" ht="80" customHeight="1" s="10">
       <c r="A85" s="3" t="inlineStr">
         <is>
           <t>wc-b2</t>
@@ -3058,7 +3107,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1" s="7">
+    <row r="86" ht="16" customHeight="1" s="10">
       <c r="A86" s="3" t="inlineStr">
         <is>
           <t>wc-t3</t>
@@ -3090,7 +3139,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="48" customHeight="1" s="7">
+    <row r="87" ht="48" customHeight="1" s="10">
       <c r="A87" s="3" t="inlineStr">
         <is>
           <t>wc-b3</t>
@@ -3122,7 +3171,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1" s="7">
+    <row r="88" ht="16" customHeight="1" s="10">
       <c r="A88" s="3" t="inlineStr">
         <is>
           <t>wc-t4</t>
@@ -3154,7 +3203,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="96" customHeight="1" s="7">
+    <row r="89" ht="96" customHeight="1" s="10">
       <c r="A89" s="3" t="inlineStr">
         <is>
           <t>wc-b4</t>
@@ -3186,7 +3235,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1" s="7">
+    <row r="90" ht="16" customHeight="1" s="10">
       <c r="A90" s="3" t="inlineStr">
         <is>
           <t>wc-t5</t>
@@ -3218,7 +3267,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="64" customHeight="1" s="7">
+    <row r="91" ht="64" customHeight="1" s="10">
       <c r="A91" s="3" t="inlineStr">
         <is>
           <t>wc-b5</t>
@@ -3250,7 +3299,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1" s="7">
+    <row r="92" ht="16" customHeight="1" s="10">
       <c r="A92" s="3" t="inlineStr">
         <is>
           <t>wc-t6</t>
@@ -3282,7 +3331,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="64" customHeight="1" s="7">
+    <row r="93" ht="64" customHeight="1" s="10">
       <c r="A93" s="3" t="inlineStr">
         <is>
           <t>wc-b6</t>
@@ -3314,14 +3363,14 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1" s="7">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="94" ht="20" customHeight="1" s="10">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>6 · Cosa facciamo</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1" s="7">
+    <row r="95" ht="16" customHeight="1" s="10">
       <c r="A95" s="3" t="inlineStr">
         <is>
           <t>stag-what</t>
@@ -3353,7 +3402,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="32" customHeight="1" s="7">
+    <row r="96" ht="32" customHeight="1" s="10">
       <c r="A96" s="3" t="inlineStr">
         <is>
           <t>sol-hl</t>
@@ -3385,7 +3434,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1" s="7">
+    <row r="97" ht="16" customHeight="1" s="10">
       <c r="A97" s="3" t="inlineStr">
         <is>
           <t>sol-1</t>
@@ -3417,7 +3466,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="16" customHeight="1" s="7">
+    <row r="98" ht="16" customHeight="1" s="10">
       <c r="A98" s="3" t="inlineStr">
         <is>
           <t>sol-2</t>
@@ -3449,7 +3498,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1" s="7">
+    <row r="99" ht="16" customHeight="1" s="10">
       <c r="A99" s="3" t="inlineStr">
         <is>
           <t>sol-3</t>
@@ -3481,7 +3530,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1" s="7">
+    <row r="100" ht="16" customHeight="1" s="10">
       <c r="A100" s="3" t="inlineStr">
         <is>
           <t>sol-4</t>
@@ -3513,7 +3562,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="32" customHeight="1" s="7">
+    <row r="101" ht="32" customHeight="1" s="10">
       <c r="A101" s="3" t="inlineStr">
         <is>
           <t>sol-5</t>
@@ -3545,7 +3594,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="32" customHeight="1" s="7">
+    <row r="102" ht="32" customHeight="1" s="10">
       <c r="A102" s="3" t="inlineStr">
         <is>
           <t>sol-6</t>
@@ -3577,821 +3626,821 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1" s="7">
-      <c r="A103" s="6" t="inlineStr">
+    <row r="103" ht="20" customHeight="1" s="10">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>7 · Processo</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1" s="7">
+    <row r="104" ht="16" customHeight="1" s="10">
       <c r="A104" s="3" t="inlineStr">
         <is>
           <t>pr-t1</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Pre-Construction &amp; Audit</t>
         </is>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>Pre-Construction &amp; Audit</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>施工前审核</t>
         </is>
       </c>
-      <c r="E104" s="11" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>Подготовка и аудит</t>
         </is>
       </c>
-      <c r="F104" s="12" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>التحضير والتدقيق</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1" s="7">
+    <row r="105" ht="16" customHeight="1" s="10">
       <c r="A105" s="3" t="inlineStr">
         <is>
           <t>pr-i1a</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Drawing &amp; spec review</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>Revisione disegni e capitolati</t>
         </is>
       </c>
-      <c r="D105" s="11" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>图纸与规范审查</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>Проверка чертежей и спецификаций</t>
         </is>
       </c>
-      <c r="F105" s="12" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>مراجعة الرسومات والمواصفات</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" s="7">
+    <row r="106" ht="16" customHeight="1" s="10">
       <c r="A106" s="3" t="inlineStr">
         <is>
           <t>pr-i1b</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Preliminary Budget</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>Budget preliminare</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>初步预算</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>Предварительный бюджет</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>الميزانية الأولية</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="16" customHeight="1" s="7">
+    <row r="107" ht="16" customHeight="1" s="10">
       <c r="A107" s="3" t="inlineStr">
         <is>
           <t>pr-i1c</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>RFI risk log</t>
         </is>
       </c>
-      <c r="C107" s="11" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>Registro RFI e rischi</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>RFI 风险记录</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>Журнал RFI и рисков</t>
         </is>
       </c>
-      <c r="F107" s="12" t="inlineStr">
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>سجل RFI والمخاطر</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="32" customHeight="1" s="7">
+    <row r="108" ht="32" customHeight="1" s="10">
       <c r="A108" s="3" t="inlineStr">
         <is>
           <t>pr-i1d</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Value engineering</t>
         </is>
       </c>
-      <c r="C108" s="11" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>Value engineering</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>价值工程</t>
         </is>
       </c>
-      <c r="E108" s="11" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>Стоимостной инжиниринг</t>
         </is>
       </c>
-      <c r="F108" s="12" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>هندسة القيمة</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1" s="7">
+    <row r="109" ht="16" customHeight="1" s="10">
       <c r="A109" s="3" t="inlineStr">
         <is>
           <t>pr-t2</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Bid &amp; Buyout</t>
         </is>
       </c>
-      <c r="C109" s="11" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>Bid &amp; Buyout</t>
         </is>
       </c>
-      <c r="D109" s="11" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>招标与采购</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>Тендер и закупки</t>
         </is>
       </c>
-      <c r="F109" s="12" t="inlineStr">
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>المناقصة والشراء</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1" s="7">
+    <row r="110" ht="16" customHeight="1" s="10">
       <c r="A110" s="3" t="inlineStr">
         <is>
           <t>pr-i2a</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Bid solicitation</t>
         </is>
       </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>Bando di gara</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>RFQ e Gara</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>招标公告</t>
         </is>
       </c>
-      <c r="E110" s="11" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>Объявление тендера</t>
         </is>
       </c>
-      <c r="F110" s="12" t="inlineStr">
+      <c r="F110" s="7" t="inlineStr">
         <is>
           <t>طرح المناقصة</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="16" customHeight="1" s="7">
+    <row r="111" ht="16" customHeight="1" s="10">
       <c r="A111" s="3" t="inlineStr">
         <is>
           <t>pr-i2b</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Subcontractor prequalification</t>
         </is>
       </c>
-      <c r="C111" s="11" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Prequalifica subappaltatori</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>分包商预审</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>Предквалификация субподрядчиков</t>
         </is>
       </c>
-      <c r="F111" s="12" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>التأهيل المسبق للمقاولين من الباطن</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1" s="7">
+    <row r="112" ht="16" customHeight="1" s="10">
       <c r="A112" s="3" t="inlineStr">
         <is>
           <t>pr-i2c</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
       </c>
-      <c r="C112" s="11" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Procurement ed equalizzazione risultati</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>报价比选</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
-        <is>
-          <t>报价比选</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
+      <c r="F112" s="7" t="inlineStr">
         <is>
           <t>Bid leveling</t>
         </is>
       </c>
-      <c r="F112" s="12" t="inlineStr">
-        <is>
-          <t>Bid leveling</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1" s="7">
+    </row>
+    <row r="113" ht="16" customHeight="1" s="10">
       <c r="A113" s="3" t="inlineStr">
         <is>
           <t>pr-i2d</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Award recommendation</t>
         </is>
       </c>
-      <c r="C113" s="11" t="inlineStr">
-        <is>
-          <t>Proposta di aggiudicazione</t>
-        </is>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Cost Engineering</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>授标建议</t>
         </is>
       </c>
-      <c r="E113" s="11" t="inlineStr">
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>Рекомендация по присуждению</t>
         </is>
       </c>
-      <c r="F113" s="12" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>توصية الإرساء</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1" s="7">
+    <row r="114" ht="16" customHeight="1" s="10">
       <c r="A114" s="3" t="inlineStr">
         <is>
           <t>pr-t3</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Contract Award</t>
         </is>
       </c>
-      <c r="C114" s="11" t="inlineStr">
-        <is>
-          <t>Aggiudicazione</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>Incarico</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>合同授予</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>Заключение договора</t>
         </is>
       </c>
-      <c r="F114" s="12" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>إرساء العقد</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1" s="7">
+    <row r="115" ht="16" customHeight="1" s="10">
       <c r="A115" s="3" t="inlineStr">
         <is>
           <t>pr-i3a</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Scope of Work review</t>
         </is>
       </c>
-      <c r="C115" s="11" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>Revisione Scope of Work</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>工作范围审查</t>
         </is>
       </c>
-      <c r="E115" s="11" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
         <is>
           <t>Проверка объёма работ</t>
         </is>
       </c>
-      <c r="F115" s="12" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>مراجعة نطاق العمل</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1" s="7">
+    <row r="116" ht="16" customHeight="1" s="10">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>pr-i3b</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="C116" s="11" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
-      <c r="F116" s="12" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>Schedule of Values</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1" s="7">
+    <row r="117" ht="16" customHeight="1" s="10">
       <c r="A117" s="3" t="inlineStr">
         <is>
           <t>pr-i3c</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>Liquidated damages</t>
         </is>
       </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>Penali contrattuali</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Sviluppo con garanzia sulle intenzioni di Design</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>违约金</t>
         </is>
       </c>
-      <c r="E117" s="11" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>Неустойка</t>
         </is>
       </c>
-      <c r="F117" s="12" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>غرامات التأخير</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1" s="7">
+    <row r="118" ht="16" customHeight="1" s="10">
       <c r="A118" s="3" t="inlineStr">
         <is>
           <t>pr-i3d</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Budget tracking</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>Budget tracking</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>预算跟踪</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>Отслеживание бюджета</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>تتبع الميزانية</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1" s="7">
+    <row r="119" ht="16" customHeight="1" s="10">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>pr-t4</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>Delivery &amp; Site</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>Delivery &amp; Cantiere</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>交付与现场</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>Поставка и объект</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>التسليم والموقع</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="16" customHeight="1" s="7">
+    <row r="120" ht="16" customHeight="1" s="10">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>pr-i4a</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>Site inspections</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>Ispezioni in loco</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>现场检查</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E120" s="6" t="inlineStr">
         <is>
           <t>Инспекции объекта</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>عمليات تفتيش الموقع</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1" s="7">
+    <row r="121" ht="16" customHeight="1" s="10">
       <c r="A121" s="3" t="inlineStr">
         <is>
           <t>pr-i4b</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>Progress meetings</t>
         </is>
       </c>
-      <c r="C121" s="11" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>Riunioni di avanzamento</t>
         </is>
       </c>
-      <c r="D121" s="11" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>进度会议</t>
         </is>
       </c>
-      <c r="E121" s="11" t="inlineStr">
+      <c r="E121" s="6" t="inlineStr">
         <is>
           <t>Совещания по ходу работ</t>
         </is>
       </c>
-      <c r="F121" s="12" t="inlineStr">
+      <c r="F121" s="7" t="inlineStr">
         <is>
           <t>اجتماعات المتابعة</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="16" customHeight="1" s="7">
+    <row r="122" ht="16" customHeight="1" s="10">
       <c r="A122" s="3" t="inlineStr">
         <is>
           <t>pr-i4c</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Change order log</t>
         </is>
       </c>
-      <c r="C122" s="11" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>Registro varianti</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>变更单记录</t>
         </is>
       </c>
-      <c r="E122" s="11" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>Журнал изменений</t>
         </is>
       </c>
-      <c r="F122" s="12" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>سجل أوامر التغيير</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1" s="7">
+    <row r="123" ht="16" customHeight="1" s="10">
       <c r="A123" s="3" t="inlineStr">
         <is>
           <t>pr-i4d</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Escalation protocol</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>Protocollo escalation</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>升级协议</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>Протокол эскалации</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr">
         <is>
           <t>بروتوكول التصعيد</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1" s="7">
+    <row r="124" ht="16" customHeight="1" s="10">
       <c r="A124" s="3" t="inlineStr">
         <is>
           <t>pr-t5</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>Closeout &amp; Turnover</t>
         </is>
       </c>
-      <c r="C124" s="11" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>Closeout &amp; Turnover</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>竣工与移交</t>
         </is>
       </c>
-      <c r="E124" s="11" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>Закрытие и передача</t>
         </is>
       </c>
-      <c r="F124" s="12" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>الإغلاق والتسليم</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1" s="7">
+    <row r="125" ht="16" customHeight="1" s="10">
       <c r="A125" s="3" t="inlineStr">
         <is>
           <t>pr-i5a</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Substantial completion</t>
         </is>
       </c>
-      <c r="C125" s="11" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>Substantial completion</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>实质性竣工</t>
         </is>
       </c>
-      <c r="E125" s="11" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>Существенное завершение</t>
         </is>
       </c>
-      <c r="F125" s="12" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr">
         <is>
           <t>الإنجاز الجوهري</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="16" customHeight="1" s="7">
+    <row r="126" ht="16" customHeight="1" s="10">
       <c r="A126" s="3" t="inlineStr">
         <is>
           <t>pr-i5b</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Punch-list</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>Punch-list</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>问题清单</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>Лист замечаний</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>قائمة النقاط المعلقة</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1" s="7">
+    <row r="127" ht="16" customHeight="1" s="10">
       <c r="A127" s="3" t="inlineStr">
         <is>
           <t>pr-i5c</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>As-built documentation</t>
         </is>
       </c>
-      <c r="C127" s="11" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>Documentazione as-built</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>竣工图文件</t>
         </is>
       </c>
-      <c r="E127" s="11" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>Исполнительная документация</t>
         </is>
       </c>
-      <c r="F127" s="12" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr">
         <is>
           <t>مخططات كما نُفِّذت</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1" s="7">
+    <row r="128" ht="16" customHeight="1" s="10">
       <c r="A128" s="3" t="inlineStr">
         <is>
           <t>pr-i5d</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Warranty &amp; O&amp;M manuals</t>
         </is>
       </c>
-      <c r="C128" s="11" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>Garanzie e manuali O&amp;M</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>保修与运维手册</t>
         </is>
       </c>
-      <c r="E128" s="11" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>Гарантии и руководства по эксплуатации</t>
         </is>
       </c>
-      <c r="F128" s="12" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>الضمانات وأدلة التشغيل والصيانة</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="20" customHeight="1" s="7">
-      <c r="A129" s="6" t="inlineStr">
+    <row r="129" ht="20" customHeight="1" s="10">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>8 · Profilo / Founder</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="16" customHeight="1" s="7">
+    <row r="130" ht="16" customHeight="1" s="10">
       <c r="A130" s="3" t="inlineStr">
         <is>
           <t>stag-who</t>
@@ -4423,7 +4472,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="409.6" customHeight="1" s="7">
+    <row r="131" ht="409.5" customHeight="1" s="10">
       <c r="A131" s="3" t="inlineStr">
         <is>
           <t>bio</t>
@@ -4455,7 +4504,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1" s="7">
+    <row r="132" ht="16" customHeight="1" s="10">
       <c r="A132" s="3" t="inlineStr">
         <is>
           <t>stag-clients</t>
@@ -4487,7 +4536,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1" s="7">
+    <row r="133" ht="16" customHeight="1" s="10">
       <c r="A133" s="3" t="inlineStr">
         <is>
           <t>clients-btn</t>
@@ -4519,14 +4568,14 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1" s="7">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="134" ht="20" customHeight="1" s="10">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>9 · Chiusura (CTA)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1" s="7">
+    <row r="135" ht="16" customHeight="1" s="10">
       <c r="A135" s="3" t="inlineStr">
         <is>
           <t>cta-hl-1</t>
@@ -4558,7 +4607,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1" s="7">
+    <row r="136" ht="16" customHeight="1" s="10">
       <c r="A136" s="3" t="inlineStr">
         <is>
           <t>cta-hl-2</t>
@@ -4590,7 +4639,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1" s="7">
+    <row r="137" ht="16" customHeight="1" s="10">
       <c r="A137" s="3" t="inlineStr">
         <is>
           <t>cta-sub</t>
@@ -4622,14 +4671,14 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="20" customHeight="1" s="7">
-      <c r="A138" s="6" t="inlineStr">
+    <row r="138" ht="20" customHeight="1" s="10">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>Area riservata (finestra password)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1" s="7">
+    <row r="139" ht="16" customHeight="1" s="10">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>pwd-title</t>
@@ -4661,7 +4710,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1" s="7">
+    <row r="140" ht="16" customHeight="1" s="10">
       <c r="A140" s="3" t="inlineStr">
         <is>
           <t>pwd-placeholder</t>
@@ -4693,7 +4742,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1" s="7">
+    <row r="141" ht="16" customHeight="1" s="10">
       <c r="A141" s="3" t="inlineStr">
         <is>
           <t>pwd-submit</t>
@@ -4730,8 +4779,8 @@
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A134:F134"/>
@@ -4743,4 +4792,152 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="10" min="1" max="1"/>
+    <col width="46" customWidth="1" style="10" min="2" max="2"/>
+    <col width="20" customWidth="1" style="10" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1" s="10">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Cifre delle statistiche — sezione «La nostra rete fornitori». Uguali in tutte le lingue: modifica SOLO la colonna «Valore». Formati: 50+, 40, €570K, €1.1M, 8–15%, ecc. Non toccare la colonna ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Statistica (dove appare)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Valore (modifica qui)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>stat-nc-t1</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Top-tier global clients  /  Clienti globali di primo piano</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>stat-nc-t2</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>International awards  /  Premi internazionali</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>40+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>stat-nc-t3</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Years of experience  /  Anni di esperienza</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>stat-nc-t4</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Documented savings — floor  /  Risparmio documentato — minimo</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>€570K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>stat-nc-t5</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Documented savings — ceiling  /  Risparmio documentato — massimo</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>€1.1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>stat-nc-t6</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Average tender savings  /  Risparmio medio in gara</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>8–15%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/_review/Potential_Revisione_Traduzioni.xlsx
+++ b/_review/Potential_Revisione_Traduzioni.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,23 +65,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00999999"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF999999"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="001E7D32"/>
-      <sz val="12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri (Corpo)"/>
+      <color rgb="001E7D32"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +126,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C71617"/>
+        <fgColor rgb="FFC71617"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,23 +155,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -172,6 +196,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -182,13 +211,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,12 +597,12 @@
   <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="10" min="1" max="1"/>
-    <col width="34" customWidth="1" style="10" min="2" max="6"/>
+    <col width="16" customWidth="1" style="13" min="1" max="1"/>
+    <col width="34" customWidth="1" style="13" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="10">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="34" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Potential — Revisione traduzioni  ·  Modifica le celle di lingua (non la colonna ID). Le righe rosse sono i titoli di sezione (ordine del sito). Simboli &lt;br&gt;/&lt;em&gt; = a capo/evidenziazioni, lasciarli.</t>
         </is>
@@ -601,14 +640,14 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" s="10">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="20" customHeight="1" s="13">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Elementi ricorrenti (scroll, footer)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="10">
+    <row r="4" ht="16" customHeight="1" s="13">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>scroll-down</t>
@@ -640,7 +679,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="10">
+    <row r="5" ht="16" customHeight="1" s="13">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>footer-copy</t>
@@ -672,7 +711,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="10">
+    <row r="6" ht="16" customHeight="1" s="13">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>footer-privacy</t>
@@ -704,14 +743,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="10">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="13">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>1 · Frase d'apertura</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="10">
+    <row r="8" ht="16" customHeight="1" s="13">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>intro-hl-1</t>
@@ -743,7 +782,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="10">
+    <row r="9" ht="16" customHeight="1" s="13">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>intro-hl-2</t>
@@ -775,7 +814,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="10">
+    <row r="10" ht="16" customHeight="1" s="13">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>intro-hl-3</t>
@@ -807,14 +846,14 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="10">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="13">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>2 · Aree di competenza</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" s="10">
+    <row r="12" ht="16" customHeight="1" s="13">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>stag-coverage</t>
@@ -846,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1" s="10">
+    <row r="13" ht="32" customHeight="1" s="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>sectors-hl</t>
@@ -878,7 +917,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" s="10">
+    <row r="14" ht="16" customHeight="1" s="13">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>s01-title</t>
@@ -910,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" s="10">
+    <row r="15" ht="16" customHeight="1" s="13">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>s01-i1</t>
@@ -942,7 +981,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="10">
+    <row r="16" ht="16" customHeight="1" s="13">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>s01-i2</t>
@@ -974,7 +1013,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" s="10">
+    <row r="17" ht="16" customHeight="1" s="13">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>s01-i3</t>
@@ -1006,7 +1045,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="10">
+    <row r="18" ht="16" customHeight="1" s="13">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>s01-i4</t>
@@ -1038,7 +1077,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" s="10">
+    <row r="19" ht="16" customHeight="1" s="13">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>s01-i5</t>
@@ -1070,7 +1109,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="10">
+    <row r="20" ht="16" customHeight="1" s="13">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>s02-title</t>
@@ -1102,7 +1141,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" s="10">
+    <row r="21" ht="16" customHeight="1" s="13">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>s02-i1</t>
@@ -1134,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1" s="10">
+    <row r="22" ht="16" customHeight="1" s="13">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>s02-i2</t>
@@ -1166,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" s="10">
+    <row r="23" ht="16" customHeight="1" s="13">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>s02-i3</t>
@@ -1198,7 +1237,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" s="10">
+    <row r="24" ht="16" customHeight="1" s="13">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>s02-i4</t>
@@ -1230,7 +1269,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" s="10">
+    <row r="25" ht="16" customHeight="1" s="13">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>s02-i5</t>
@@ -1262,7 +1301,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" s="10">
+    <row r="26" ht="16" customHeight="1" s="13">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>s03-title</t>
@@ -1294,7 +1333,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1" s="10">
+    <row r="27" ht="16" customHeight="1" s="13">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>s03-i1</t>
@@ -1326,7 +1365,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1" s="10">
+    <row r="28" ht="16" customHeight="1" s="13">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>s03-i2</t>
@@ -1358,7 +1397,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1" s="10">
+    <row r="29" ht="16" customHeight="1" s="13">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>s03-i3</t>
@@ -1390,7 +1429,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="10">
+    <row r="30" ht="16" customHeight="1" s="13">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>s03-i4</t>
@@ -1422,7 +1461,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" s="10">
+    <row r="31" ht="16" customHeight="1" s="13">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>s03-i5</t>
@@ -1454,7 +1493,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1" s="10">
+    <row r="32" ht="16" customHeight="1" s="13">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>s03-i6</t>
@@ -1486,7 +1525,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" s="10">
+    <row r="33" ht="16" customHeight="1" s="13">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>s03-i7</t>
@@ -1518,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" s="10">
+    <row r="34" ht="16" customHeight="1" s="13">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>s04-title</t>
@@ -1550,7 +1589,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1" s="10">
+    <row r="35" ht="16" customHeight="1" s="13">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>s04-i1</t>
@@ -1582,7 +1621,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1" s="10">
+    <row r="36" ht="16" customHeight="1" s="13">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>s04-i2</t>
@@ -1614,7 +1653,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1" s="10">
+    <row r="37" ht="16" customHeight="1" s="13">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>s04-i3</t>
@@ -1646,7 +1685,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1" s="10">
+    <row r="38" ht="16" customHeight="1" s="13">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>s04-i4</t>
@@ -1678,7 +1717,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1" s="10">
+    <row r="39" ht="16" customHeight="1" s="13">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>s05-title</t>
@@ -1710,7 +1749,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" s="10">
+    <row r="40" ht="16" customHeight="1" s="13">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>s05-i1</t>
@@ -1742,7 +1781,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" s="10">
+    <row r="41" ht="16" customHeight="1" s="13">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>s05-i2</t>
@@ -1774,7 +1813,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1" s="10">
+    <row r="42" ht="16" customHeight="1" s="13">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>s05-i3</t>
@@ -1806,7 +1845,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1" s="10">
+    <row r="43" ht="16" customHeight="1" s="13">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>s05-i4</t>
@@ -1838,7 +1877,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1" s="10">
+    <row r="44" ht="16" customHeight="1" s="13">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>s06-title</t>
@@ -1870,7 +1909,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1" s="10">
+    <row r="45" ht="16" customHeight="1" s="13">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>s06-i1</t>
@@ -1902,7 +1941,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1" s="10">
+    <row r="46" ht="16" customHeight="1" s="13">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>s06-i2</t>
@@ -1934,7 +1973,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1" s="10">
+    <row r="47" ht="16" customHeight="1" s="13">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>s06-i3</t>
@@ -1966,7 +2005,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1" s="10">
+    <row r="48" ht="16" customHeight="1" s="13">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>s06-i4</t>
@@ -1998,7 +2037,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1" s="10">
+    <row r="49" ht="16" customHeight="1" s="13">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>s07-title</t>
@@ -2030,7 +2069,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1" s="10">
+    <row r="50" ht="16" customHeight="1" s="13">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>s07-i1</t>
@@ -2062,7 +2101,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1" s="10">
+    <row r="51" ht="32" customHeight="1" s="13">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>s07-i2</t>
@@ -2094,7 +2133,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="32" customHeight="1" s="10">
+    <row r="52" ht="32" customHeight="1" s="13">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>s07-i3</t>
@@ -2126,7 +2165,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1" s="10">
+    <row r="53" ht="32" customHeight="1" s="13">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>s07-i4</t>
@@ -2158,7 +2197,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1" s="10">
+    <row r="54" ht="16" customHeight="1" s="13">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>s07-i5</t>
@@ -2190,7 +2229,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1" s="10">
+    <row r="55" ht="16" customHeight="1" s="13">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>s07-i6</t>
@@ -2222,14 +2261,14 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1" s="10">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="56" ht="20" customHeight="1" s="13">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>3 · Il problema</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1" s="10">
+    <row r="57" ht="16" customHeight="1" s="13">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>stag-problem</t>
@@ -2261,7 +2300,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="64" customHeight="1" s="10">
+    <row r="58" ht="64" customHeight="1" s="13">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>problem-big</t>
@@ -2293,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1" s="10">
+    <row r="59" ht="16" customHeight="1" s="13">
       <c r="A59" s="3" t="inlineStr">
         <is>
           <t>prob-tag1</t>
@@ -2325,7 +2364,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="64" customHeight="1" s="10">
+    <row r="60" ht="64" customHeight="1" s="13">
       <c r="A60" s="3" t="inlineStr">
         <is>
           <t>prob-txt1</t>
@@ -2357,7 +2396,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1" s="10">
+    <row r="61" ht="16" customHeight="1" s="13">
       <c r="A61" s="3" t="inlineStr">
         <is>
           <t>prob-tag2</t>
@@ -2389,7 +2428,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="64" customHeight="1" s="10">
+    <row r="62" ht="64" customHeight="1" s="13">
       <c r="A62" s="3" t="inlineStr">
         <is>
           <t>prob-txt2</t>
@@ -2421,7 +2460,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1" s="10">
+    <row r="63" ht="16" customHeight="1" s="13">
       <c r="A63" s="3" t="inlineStr">
         <is>
           <t>prob-tag3</t>
@@ -2453,7 +2492,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="64" customHeight="1" s="10">
+    <row r="64" ht="64" customHeight="1" s="13">
       <c r="A64" s="3" t="inlineStr">
         <is>
           <t>prob-txt3</t>
@@ -2485,46 +2524,46 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1" s="10">
-      <c r="A65" s="9" t="inlineStr">
+    <row r="65" ht="20" customHeight="1" s="13">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>4 · I numeri</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1" s="10">
+    <row r="66" ht="16" customHeight="1" s="13">
       <c r="A66" s="3" t="inlineStr">
         <is>
           <t>stag-numbers</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Our supplier network</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>Our numbers</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>I nostri numeri</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>我们的供应商网络</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>Наша сеть поставщиков</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>شبكة موردينا</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="32" customHeight="1" s="10">
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>我们的数据</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Наши цифры</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>أرقامنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1" s="13">
       <c r="A67" s="3" t="inlineStr">
         <is>
           <t>num-hl</t>
@@ -2556,7 +2595,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1" s="10">
+    <row r="68" ht="16" customHeight="1" s="13">
       <c r="A68" s="3" t="inlineStr">
         <is>
           <t>nc-t1</t>
@@ -2588,7 +2627,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1" s="10">
+    <row r="69" ht="16" customHeight="1" s="13">
       <c r="A69" s="3" t="inlineStr">
         <is>
           <t>nc-d1</t>
@@ -2620,7 +2659,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1" s="10">
+    <row r="70" ht="16" customHeight="1" s="13">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>nc-t2</t>
@@ -2652,7 +2691,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1" s="10">
+    <row r="71" ht="16" customHeight="1" s="13">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>nc-d2</t>
@@ -2684,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1" s="10">
+    <row r="72" ht="16" customHeight="1" s="13">
       <c r="A72" s="3" t="inlineStr">
         <is>
           <t>nc-t3</t>
@@ -2716,7 +2755,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1" s="10">
+    <row r="73" ht="16" customHeight="1" s="13">
       <c r="A73" s="3" t="inlineStr">
         <is>
           <t>nc-d3</t>
@@ -2748,7 +2787,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1" s="10">
+    <row r="74" ht="16" customHeight="1" s="13">
       <c r="A74" s="3" t="inlineStr">
         <is>
           <t>nc-t4</t>
@@ -2780,7 +2819,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1" s="10">
+    <row r="75" ht="16" customHeight="1" s="13">
       <c r="A75" s="3" t="inlineStr">
         <is>
           <t>nc-d4</t>
@@ -2812,7 +2851,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1" s="10">
+    <row r="76" ht="16" customHeight="1" s="13">
       <c r="A76" s="3" t="inlineStr">
         <is>
           <t>nc-t5</t>
@@ -2844,7 +2883,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1" s="10">
+    <row r="77" ht="16" customHeight="1" s="13">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>nc-d5</t>
@@ -2876,7 +2915,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1" s="10">
+    <row r="78" ht="16" customHeight="1" s="13">
       <c r="A78" s="3" t="inlineStr">
         <is>
           <t>nc-t6</t>
@@ -2908,7 +2947,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1" s="10">
+    <row r="79" ht="16" customHeight="1" s="13">
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>nc-d6</t>
@@ -2940,14 +2979,14 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1" s="10">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="80" ht="20" customHeight="1" s="13">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>5 · Perché funziona</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1" s="10">
+    <row r="81" ht="16" customHeight="1" s="13">
       <c r="A81" s="3" t="inlineStr">
         <is>
           <t>stag-why</t>
@@ -2979,7 +3018,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1" s="10">
+    <row r="82" ht="16" customHeight="1" s="13">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>wc-t1</t>
@@ -3011,7 +3050,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="64" customHeight="1" s="10">
+    <row r="83" ht="64" customHeight="1" s="13">
       <c r="A83" s="3" t="inlineStr">
         <is>
           <t>wc-b1</t>
@@ -3043,7 +3082,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="16" customHeight="1" s="10">
+    <row r="84" ht="16" customHeight="1" s="13">
       <c r="A84" s="3" t="inlineStr">
         <is>
           <t>wc-t2</t>
@@ -3075,7 +3114,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="80" customHeight="1" s="10">
+    <row r="85" ht="80" customHeight="1" s="13">
       <c r="A85" s="3" t="inlineStr">
         <is>
           <t>wc-b2</t>
@@ -3107,7 +3146,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1" s="10">
+    <row r="86" ht="16" customHeight="1" s="13">
       <c r="A86" s="3" t="inlineStr">
         <is>
           <t>wc-t3</t>
@@ -3139,7 +3178,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="48" customHeight="1" s="10">
+    <row r="87" ht="48" customHeight="1" s="13">
       <c r="A87" s="3" t="inlineStr">
         <is>
           <t>wc-b3</t>
@@ -3171,7 +3210,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1" s="10">
+    <row r="88" ht="16" customHeight="1" s="13">
       <c r="A88" s="3" t="inlineStr">
         <is>
           <t>wc-t4</t>
@@ -3203,7 +3242,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="96" customHeight="1" s="10">
+    <row r="89" ht="96" customHeight="1" s="13">
       <c r="A89" s="3" t="inlineStr">
         <is>
           <t>wc-b4</t>
@@ -3235,7 +3274,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1" s="10">
+    <row r="90" ht="16" customHeight="1" s="13">
       <c r="A90" s="3" t="inlineStr">
         <is>
           <t>wc-t5</t>
@@ -3267,7 +3306,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="64" customHeight="1" s="10">
+    <row r="91" ht="64" customHeight="1" s="13">
       <c r="A91" s="3" t="inlineStr">
         <is>
           <t>wc-b5</t>
@@ -3299,7 +3338,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1" s="10">
+    <row r="92" ht="16" customHeight="1" s="13">
       <c r="A92" s="3" t="inlineStr">
         <is>
           <t>wc-t6</t>
@@ -3331,7 +3370,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="64" customHeight="1" s="10">
+    <row r="93" ht="64" customHeight="1" s="13">
       <c r="A93" s="3" t="inlineStr">
         <is>
           <t>wc-b6</t>
@@ -3363,14 +3402,14 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1" s="10">
-      <c r="A94" s="9" t="inlineStr">
+    <row r="94" ht="20" customHeight="1" s="13">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>6 · Cosa facciamo</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1" s="10">
+    <row r="95" ht="16" customHeight="1" s="13">
       <c r="A95" s="3" t="inlineStr">
         <is>
           <t>stag-what</t>
@@ -3402,7 +3441,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="32" customHeight="1" s="10">
+    <row r="96" ht="32" customHeight="1" s="13">
       <c r="A96" s="3" t="inlineStr">
         <is>
           <t>sol-hl</t>
@@ -3434,7 +3473,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1" s="10">
+    <row r="97" ht="16" customHeight="1" s="13">
       <c r="A97" s="3" t="inlineStr">
         <is>
           <t>sol-1</t>
@@ -3466,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="16" customHeight="1" s="10">
+    <row r="98" ht="16" customHeight="1" s="13">
       <c r="A98" s="3" t="inlineStr">
         <is>
           <t>sol-2</t>
@@ -3498,7 +3537,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1" s="10">
+    <row r="99" ht="16" customHeight="1" s="13">
       <c r="A99" s="3" t="inlineStr">
         <is>
           <t>sol-3</t>
@@ -3530,7 +3569,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1" s="10">
+    <row r="100" ht="16" customHeight="1" s="13">
       <c r="A100" s="3" t="inlineStr">
         <is>
           <t>sol-4</t>
@@ -3562,7 +3601,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="32" customHeight="1" s="10">
+    <row r="101" ht="32" customHeight="1" s="13">
       <c r="A101" s="3" t="inlineStr">
         <is>
           <t>sol-5</t>
@@ -3594,7 +3633,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="32" customHeight="1" s="10">
+    <row r="102" ht="32" customHeight="1" s="13">
       <c r="A102" s="3" t="inlineStr">
         <is>
           <t>sol-6</t>
@@ -3626,14 +3665,14 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1" s="10">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="103" ht="20" customHeight="1" s="13">
+      <c r="A103" s="12" t="inlineStr">
         <is>
           <t>7 · Processo</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1" s="10">
+    <row r="104" ht="16" customHeight="1" s="13">
       <c r="A104" s="3" t="inlineStr">
         <is>
           <t>pr-t1</t>
@@ -3665,7 +3704,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1" s="10">
+    <row r="105" ht="16" customHeight="1" s="13">
       <c r="A105" s="3" t="inlineStr">
         <is>
           <t>pr-i1a</t>
@@ -3697,7 +3736,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" s="10">
+    <row r="106" ht="16" customHeight="1" s="13">
       <c r="A106" s="3" t="inlineStr">
         <is>
           <t>pr-i1b</t>
@@ -3729,7 +3768,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="16" customHeight="1" s="10">
+    <row r="107" ht="16" customHeight="1" s="13">
       <c r="A107" s="3" t="inlineStr">
         <is>
           <t>pr-i1c</t>
@@ -3761,7 +3800,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="32" customHeight="1" s="10">
+    <row r="108" ht="32" customHeight="1" s="13">
       <c r="A108" s="3" t="inlineStr">
         <is>
           <t>pr-i1d</t>
@@ -3793,7 +3832,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1" s="10">
+    <row r="109" ht="16" customHeight="1" s="13">
       <c r="A109" s="3" t="inlineStr">
         <is>
           <t>pr-t2</t>
@@ -3825,39 +3864,39 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1" s="10">
+    <row r="110" ht="16" customHeight="1" s="13">
       <c r="A110" s="3" t="inlineStr">
         <is>
           <t>pr-i2a</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>Bid solicitation</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>RFQ &amp; tender</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
         <is>
           <t>RFQ e Gara</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>招标公告</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>Объявление тендера</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>طرح المناقصة</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1" s="10">
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>询价与招标</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Запрос цен и тендер</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="inlineStr">
+        <is>
+          <t>طلب عروض الأسعار والمناقصة</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1" s="13">
       <c r="A111" s="3" t="inlineStr">
         <is>
           <t>pr-i2b</t>
@@ -3889,71 +3928,71 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1" s="10">
+    <row r="112" ht="16" customHeight="1" s="13">
       <c r="A112" s="3" t="inlineStr">
         <is>
           <t>pr-i2c</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>Bid leveling</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Procurement &amp; bid leveling</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
         <is>
           <t>Procurement ed equalizzazione risultati</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>报价比选</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>Bid leveling</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>Bid leveling</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1" s="10">
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>采购与报价比选</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>Закупки и выравнивание предложений</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>المشتريات وتسوية العطاءات</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1" s="13">
       <c r="A113" s="3" t="inlineStr">
         <is>
           <t>pr-i2d</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>Award recommendation</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="B113" s="20" t="inlineStr">
+        <is>
+          <t>Cost engineering</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="inlineStr">
         <is>
           <t>Cost Engineering</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>授标建议</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>Рекомендация по присуждению</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>توصية الإرساء</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1" s="10">
+      <c r="D113" s="20" t="inlineStr">
+        <is>
+          <t>成本工程</t>
+        </is>
+      </c>
+      <c r="E113" s="20" t="inlineStr">
+        <is>
+          <t>Стоимостной инжиниринг</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>هندسة التكلفة</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="16" customHeight="1" s="13">
       <c r="A114" s="3" t="inlineStr">
         <is>
           <t>pr-t3</t>
@@ -3964,7 +4003,7 @@
           <t>Contract Award</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C114" s="18" t="inlineStr">
         <is>
           <t>Incarico</t>
         </is>
@@ -3985,7 +4024,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1" s="10">
+    <row r="115" ht="16" customHeight="1" s="13">
       <c r="A115" s="3" t="inlineStr">
         <is>
           <t>pr-i3a</t>
@@ -4017,7 +4056,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1" s="10">
+    <row r="116" ht="16" customHeight="1" s="13">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>pr-i3b</t>
@@ -4049,39 +4088,39 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1" s="10">
+    <row r="117" ht="16" customHeight="1" s="13">
       <c r="A117" s="3" t="inlineStr">
         <is>
           <t>pr-i3c</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>Liquidated damages</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>Design-intent assurance</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
         <is>
           <t>Sviluppo con garanzia sulle intenzioni di Design</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>违约金</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>Неустойка</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>غرامات التأخير</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1" s="10">
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>设计意图保障</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>Сохранение проектного замысла</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>ضمان مقصد التصميم</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1" s="13">
       <c r="A118" s="3" t="inlineStr">
         <is>
           <t>pr-i3d</t>
@@ -4113,7 +4152,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1" s="10">
+    <row r="119" ht="16" customHeight="1" s="13">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>pr-t4</t>
@@ -4145,7 +4184,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="16" customHeight="1" s="10">
+    <row r="120" ht="16" customHeight="1" s="13">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>pr-i4a</t>
@@ -4177,7 +4216,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1" s="10">
+    <row r="121" ht="16" customHeight="1" s="13">
       <c r="A121" s="3" t="inlineStr">
         <is>
           <t>pr-i4b</t>
@@ -4209,7 +4248,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="16" customHeight="1" s="10">
+    <row r="122" ht="16" customHeight="1" s="13">
       <c r="A122" s="3" t="inlineStr">
         <is>
           <t>pr-i4c</t>
@@ -4241,7 +4280,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1" s="10">
+    <row r="123" ht="16" customHeight="1" s="13">
       <c r="A123" s="3" t="inlineStr">
         <is>
           <t>pr-i4d</t>
@@ -4273,7 +4312,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1" s="10">
+    <row r="124" ht="16" customHeight="1" s="13">
       <c r="A124" s="3" t="inlineStr">
         <is>
           <t>pr-t5</t>
@@ -4305,7 +4344,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1" s="10">
+    <row r="125" ht="16" customHeight="1" s="13">
       <c r="A125" s="3" t="inlineStr">
         <is>
           <t>pr-i5a</t>
@@ -4337,7 +4376,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="16" customHeight="1" s="10">
+    <row r="126" ht="16" customHeight="1" s="13">
       <c r="A126" s="3" t="inlineStr">
         <is>
           <t>pr-i5b</t>
@@ -4369,7 +4408,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1" s="10">
+    <row r="127" ht="16" customHeight="1" s="13">
       <c r="A127" s="3" t="inlineStr">
         <is>
           <t>pr-i5c</t>
@@ -4401,7 +4440,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1" s="10">
+    <row r="128" ht="16" customHeight="1" s="13">
       <c r="A128" s="3" t="inlineStr">
         <is>
           <t>pr-i5d</t>
@@ -4433,14 +4472,14 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="20" customHeight="1" s="10">
-      <c r="A129" s="9" t="inlineStr">
+    <row r="129" ht="20" customHeight="1" s="13">
+      <c r="A129" s="12" t="inlineStr">
         <is>
           <t>8 · Profilo / Founder</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="16" customHeight="1" s="10">
+    <row r="130" ht="16" customHeight="1" s="13">
       <c r="A130" s="3" t="inlineStr">
         <is>
           <t>stag-who</t>
@@ -4472,7 +4511,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="409.5" customHeight="1" s="10">
+    <row r="131" ht="409.5" customHeight="1" s="13">
       <c r="A131" s="3" t="inlineStr">
         <is>
           <t>bio</t>
@@ -4504,7 +4543,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1" s="10">
+    <row r="132" ht="16" customHeight="1" s="13">
       <c r="A132" s="3" t="inlineStr">
         <is>
           <t>stag-clients</t>
@@ -4536,7 +4575,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1" s="10">
+    <row r="133" ht="16" customHeight="1" s="13">
       <c r="A133" s="3" t="inlineStr">
         <is>
           <t>clients-btn</t>
@@ -4568,14 +4607,14 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1" s="10">
-      <c r="A134" s="9" t="inlineStr">
+    <row r="134" ht="20" customHeight="1" s="13">
+      <c r="A134" s="12" t="inlineStr">
         <is>
           <t>9 · Chiusura (CTA)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1" s="10">
+    <row r="135" ht="16" customHeight="1" s="13">
       <c r="A135" s="3" t="inlineStr">
         <is>
           <t>cta-hl-1</t>
@@ -4607,7 +4646,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1" s="10">
+    <row r="136" ht="16" customHeight="1" s="13">
       <c r="A136" s="3" t="inlineStr">
         <is>
           <t>cta-hl-2</t>
@@ -4639,7 +4678,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1" s="10">
+    <row r="137" ht="16" customHeight="1" s="13">
       <c r="A137" s="3" t="inlineStr">
         <is>
           <t>cta-sub</t>
@@ -4671,14 +4710,14 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="20" customHeight="1" s="10">
-      <c r="A138" s="9" t="inlineStr">
+    <row r="138" ht="20" customHeight="1" s="13">
+      <c r="A138" s="12" t="inlineStr">
         <is>
           <t>Area riservata (finestra password)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1" s="10">
+    <row r="139" ht="16" customHeight="1" s="13">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>pwd-title</t>
@@ -4710,7 +4749,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1" s="10">
+    <row r="140" ht="16" customHeight="1" s="13">
       <c r="A140" s="3" t="inlineStr">
         <is>
           <t>pwd-placeholder</t>
@@ -4742,7 +4781,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1" s="10">
+    <row r="141" ht="16" customHeight="1" s="13">
       <c r="A141" s="3" t="inlineStr">
         <is>
           <t>pwd-submit</t>
@@ -4779,8 +4818,8 @@
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A134:F134"/>
@@ -4801,44 +4840,44 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="10" min="1" max="1"/>
-    <col width="46" customWidth="1" style="10" min="2" max="2"/>
-    <col width="20" customWidth="1" style="10" min="3" max="3"/>
+    <col width="16" customWidth="1" style="13" min="1" max="1"/>
+    <col width="46" customWidth="1" style="13" min="2" max="2"/>
+    <col width="20" customWidth="1" style="13" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" s="10">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="42" customHeight="1" s="13">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Cifre delle statistiche — sezione «La nostra rete fornitori». Uguali in tutte le lingue: modifica SOLO la colonna «Valore». Formati: 50+, 40, €570K, €1.1M, 8–15%, ecc. Non toccare la colonna ID.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Statistica (dove appare)</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Valore (modifica qui)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="3" ht="16" customHeight="1" s="13">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>stat-nc-t1</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Top-tier global clients  /  Clienti globali di primo piano</t>
         </is>
@@ -4849,13 +4888,13 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="13">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>stat-nc-t2</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>International awards  /  Premi internazionali</t>
         </is>
@@ -4866,13 +4905,13 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="16" customHeight="1" s="13">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>stat-nc-t3</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Years of experience  /  Anni di esperienza</t>
         </is>
@@ -4883,13 +4922,13 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="32" customHeight="1" s="13">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>stat-nc-t4</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Documented savings — floor  /  Risparmio documentato — minimo</t>
         </is>
@@ -4900,13 +4939,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="32" customHeight="1" s="13">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>stat-nc-t5</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Documented savings — ceiling  /  Risparmio documentato — massimo</t>
         </is>
@@ -4917,13 +4956,13 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="16" customHeight="1" s="13">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>stat-nc-t6</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Average tender savings  /  Risparmio medio in gara</t>
         </is>

--- a/_review/Potential_Revisione_Traduzioni.xlsx
+++ b/_review/Potential_Revisione_Traduzioni.xlsx
@@ -3821,9 +3821,9 @@
           <t>价值工程</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Стоимостной инжиниринг</t>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Функционально-стоимостной инжиниринг</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -3998,9 +3998,9 @@
           <t>pr-t3</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>Contract Award</t>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="C114" s="18" t="inlineStr">
@@ -4008,19 +4008,19 @@
           <t>Incarico</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>合同授予</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Заключение договора</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>إرساء العقد</t>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>委任</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Поручение</t>
+        </is>
+      </c>
+      <c r="F114" s="21" t="inlineStr">
+        <is>
+          <t>التكليف</t>
         </is>
       </c>
     </row>
@@ -4818,8 +4818,8 @@
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A134:F134"/>
